--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote Comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +80,14 @@
       <color rgb="002E7D32"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -125,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,6 +160,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -225,6 +236,315 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Per job: actual cost vs price sold (iQuote) vs SPOT would-be price</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$4:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$C$4:$C$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$D$4:$D$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Estimate accuracy vs actual cost by category (8 jobs, excl blowout) — closer to Actual = better</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!B15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$16:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$16:$B$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!C15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$16:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$C$16:$C$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!D15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$16:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$D$16:$D$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4755,4 +5075,268 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Ground-Truth Charts — 9 produced jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>MIS Job</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Actual Cost $</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sold (iQuote) $</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SPOT Would-Be $</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>236341</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2277</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1733</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>236355</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>194</v>
+      </c>
+      <c r="C5" t="n">
+        <v>242</v>
+      </c>
+      <c r="D5" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>236550</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>236688</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>207</v>
+      </c>
+      <c r="C7" t="n">
+        <v>248</v>
+      </c>
+      <c r="D7" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>236802</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4859</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6164</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>236822</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>926</v>
+      </c>
+      <c r="C9" t="n">
+        <v>985</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>236943</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9468</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6774</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>236869</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2580</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2876</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>237252</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>164</v>
+      </c>
+      <c r="C12" t="n">
+        <v>142</v>
+      </c>
+      <c r="D12" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Actual $</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SPOT est $</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>iQuote est $</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2690</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2972</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4541</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3916</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3108</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1966</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1825</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -250,7 +250,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Per job: actual cost vs price sold (iQuote) vs SPOT would-be price</a:t>
+              <a:t>Per job: actual production cost vs invoiced vs iQuote quoted vs SPOT quoted</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -332,6 +332,30 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$4:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$E$4:$E$12</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -380,7 +404,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Estimate accuracy vs actual cost by category (8 jobs, excl blowout) — closer to Actual = better</a:t>
+              <a:t>Estimated COST accuracy vs actual by category (8 jobs, excl blowout) — closer to Actual = better</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -502,12 +526,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3600000"/>
+    <ext cx="7920000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -524,12 +548,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3600000"/>
+    <ext cx="7920000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -857,6 +881,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -916,19 +941,19 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Sold (iQuote prices) vs actual cost</t>
+          <t>Invoiced vs actual cost</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>$18,131 sold / $22,305 cost = -23% margin</t>
+          <t>$18,131 invoiced / $22,305 cost = -23% margin</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Jobs that lost money as sold</t>
+          <t>Jobs that lost money as invoiced</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -5083,13 +5108,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5105,19 +5131,24 @@
           <t>MIS Job</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Actual Cost $</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sold (iQuote) $</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SPOT Would-Be $</t>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Invoiced $</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>iQuote Quote $</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>SPOT Quote $</t>
         </is>
       </c>
     </row>
@@ -5134,6 +5165,9 @@
         <v>1733</v>
       </c>
       <c r="D4" t="n">
+        <v>1733</v>
+      </c>
+      <c r="E4" t="n">
         <v>1753</v>
       </c>
     </row>
@@ -5150,6 +5184,9 @@
         <v>242</v>
       </c>
       <c r="D5" t="n">
+        <v>242</v>
+      </c>
+      <c r="E5" t="n">
         <v>454</v>
       </c>
     </row>
@@ -5166,6 +5203,9 @@
         <v>1387</v>
       </c>
       <c r="D6" t="n">
+        <v>1387</v>
+      </c>
+      <c r="E6" t="n">
         <v>1754</v>
       </c>
     </row>
@@ -5182,6 +5222,9 @@
         <v>248</v>
       </c>
       <c r="D7" t="n">
+        <v>248</v>
+      </c>
+      <c r="E7" t="n">
         <v>256</v>
       </c>
     </row>
@@ -5198,6 +5241,9 @@
         <v>6164</v>
       </c>
       <c r="D8" t="n">
+        <v>6164</v>
+      </c>
+      <c r="E8" t="n">
         <v>5824</v>
       </c>
     </row>
@@ -5214,6 +5260,9 @@
         <v>985</v>
       </c>
       <c r="D9" t="n">
+        <v>985</v>
+      </c>
+      <c r="E9" t="n">
         <v>1259</v>
       </c>
     </row>
@@ -5230,6 +5279,9 @@
         <v>4353</v>
       </c>
       <c r="D10" t="n">
+        <v>3695</v>
+      </c>
+      <c r="E10" t="n">
         <v>6774</v>
       </c>
     </row>
@@ -5246,6 +5298,9 @@
         <v>2876</v>
       </c>
       <c r="D11" t="n">
+        <v>2749</v>
+      </c>
+      <c r="E11" t="n">
         <v>3071</v>
       </c>
     </row>
@@ -5262,6 +5317,9 @@
         <v>142</v>
       </c>
       <c r="D12" t="n">
+        <v>131</v>
+      </c>
+      <c r="E12" t="n">
         <v>132</v>
       </c>
     </row>
@@ -5271,17 +5329,17 @@
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Actual $</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>SPOT est $</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>iQuote est $</t>
         </is>

--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -250,7 +250,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Per job: actual production cost vs invoiced vs iQuote quoted vs SPOT quoted</a:t>
+              <a:t>Actual invoice vs iQuote sell vs SPOT sell</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -332,30 +332,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'Charts'!E3</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Charts'!$A$4:$A$12</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Charts'!$E$4:$E$12</f>
-            </numRef>
-          </val>
-        </ser>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -404,7 +380,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Estimated COST accuracy vs actual by category (8 jobs, excl blowout) — closer to Actual = better</a:t>
+              <a:t>Estimated COST accuracy vs actual by category (8 jobs, excl blowout)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -526,7 +502,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -548,7 +524,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>23</row>
       <rowOff>0</rowOff>
@@ -881,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5108,20 +5083,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>Ground-Truth Charts — 9 produced jobs</t>
+          <t>Price Comparison — 9 produced jobs</t>
         </is>
       </c>
     </row>
@@ -5133,22 +5107,17 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>Actual Cost $</t>
+          <t>Actual Invoice $</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>Invoiced $</t>
+          <t>iQuote Sell $</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>iQuote Quote $</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>SPOT Quote $</t>
+          <t>SPOT Sell $</t>
         </is>
       </c>
     </row>
@@ -5159,15 +5128,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2277</v>
+        <v>1733</v>
       </c>
       <c r="C4" t="n">
         <v>1733</v>
       </c>
       <c r="D4" t="n">
-        <v>1733</v>
-      </c>
-      <c r="E4" t="n">
         <v>1753</v>
       </c>
     </row>
@@ -5178,15 +5144,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="C5" t="n">
         <v>242</v>
       </c>
       <c r="D5" t="n">
-        <v>242</v>
-      </c>
-      <c r="E5" t="n">
         <v>454</v>
       </c>
     </row>
@@ -5197,15 +5160,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1631</v>
+        <v>1387</v>
       </c>
       <c r="C6" t="n">
         <v>1387</v>
       </c>
       <c r="D6" t="n">
-        <v>1387</v>
-      </c>
-      <c r="E6" t="n">
         <v>1754</v>
       </c>
     </row>
@@ -5216,15 +5176,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="C7" t="n">
         <v>248</v>
       </c>
       <c r="D7" t="n">
-        <v>248</v>
-      </c>
-      <c r="E7" t="n">
         <v>256</v>
       </c>
     </row>
@@ -5235,15 +5192,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4859</v>
+        <v>6164</v>
       </c>
       <c r="C8" t="n">
         <v>6164</v>
       </c>
       <c r="D8" t="n">
-        <v>6164</v>
-      </c>
-      <c r="E8" t="n">
         <v>5824</v>
       </c>
     </row>
@@ -5254,15 +5208,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>926</v>
+        <v>985</v>
       </c>
       <c r="C9" t="n">
         <v>985</v>
       </c>
       <c r="D9" t="n">
-        <v>985</v>
-      </c>
-      <c r="E9" t="n">
         <v>1259</v>
       </c>
     </row>
@@ -5273,15 +5224,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9468</v>
+        <v>4353</v>
       </c>
       <c r="C10" t="n">
-        <v>4353</v>
+        <v>3695</v>
       </c>
       <c r="D10" t="n">
-        <v>3695</v>
-      </c>
-      <c r="E10" t="n">
         <v>6774</v>
       </c>
     </row>
@@ -5292,15 +5240,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2580</v>
+        <v>2876</v>
       </c>
       <c r="C11" t="n">
-        <v>2876</v>
+        <v>2749</v>
       </c>
       <c r="D11" t="n">
-        <v>2749</v>
-      </c>
-      <c r="E11" t="n">
         <v>3071</v>
       </c>
     </row>
@@ -5311,15 +5256,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
-      </c>
-      <c r="E12" t="n">
         <v>132</v>
       </c>
     </row>

--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -1147,17 +1147,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>SPOT $</t>
+          <t>SPOT Sell $</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>SPOT $/ea</t>
+          <t>SPOT Sell $/ea</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>iQuote $</t>
+          <t>iQuote Sell $</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">

--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,11 +82,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -134,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,7 +156,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -985,7 +979,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Cutting</t>
@@ -993,7 +987,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Both under: SPOT -32%, iQuote -41%. Root cause found (see Cutting tab): assumed cut speed 650 in/min vs ~165 real. Calibration fix identified, BOOKMARKED pending leadership review</t>
+          <t>Both under: SPOT -32%, iQuote -41%. Root cause found (see detailed workbook): assumed cut speed 650 in/min (inherited from legacy) vs ~165 real. Fix identified, BOOKMARKED pending leadership review</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1047,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cutting throughput is the one systematic gap — in BOTH systems. Fix is two admin-console values in SPOT (no code); recommendation bookmarked.</t>
+          <t>Cutting throughput is the one systematic gap — in BOTH systems, inherited from legacy. Fix is two admin-console values in SPOT (no code); recommendation bookmarked.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1076,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B21:E21"/>
@@ -1100,16 +1095,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J257"/>
+  <dimension ref="A1:J247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
@@ -1125,7 +1120,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Grouped by SPOT project. Component specs from the estimate; iQuote price and actuals compared at quote/quantity level. Δ% = SPOT vs iQuote (+ = SPOT higher).</t>
+          <t>Grouped by SPOT project. All $ are SELL prices. Component-level iQuote prices auto-matched by product name + qty (blank = no confident 1:1 match; totals always compare). Δ% = SPOT vs iQuote (+ = SPOT higher).</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1179,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Strat Pro Buttermelt PDQ - 2nd Grouping   —   SPOT RW-260622-133707  ·  iQuote #222085</t>
+          <t>Strat Pro Buttermelt PDQ - 2nd Grouping:   SPOT RW-260622-133707  ·  iQuote #222085</t>
         </is>
       </c>
     </row>
@@ -1208,6 +1203,17 @@
       <c r="E6" s="9" t="n">
         <v>5.687</v>
       </c>
+      <c r="F6" s="9" t="n">
+        <v>5749.66</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>-2820.9</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>-49.1%</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1229,6 +1235,17 @@
       <c r="E7" s="9" t="n">
         <v>4.442</v>
       </c>
+      <c r="F7" s="9" t="n">
+        <v>2045.03</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>242.56</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>+11.9%</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1250,6 +1267,17 @@
       <c r="E8" s="9" t="n">
         <v>1.063</v>
       </c>
+      <c r="F8" s="9" t="n">
+        <v>323.78</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>223.69</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>+69.1%</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1280,7 +1308,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>PO 47928 / MTD 645-90566A   —   SPOT RW-260623-091031  ·  iQuote #223207  ·  BECAME A JOB</t>
+          <t>PO 47928 / MTD 645-90566A:   SPOT RW-260623-091031  ·  iQuote #223207  ·  BECAME A JOB</t>
         </is>
       </c>
     </row>
@@ -1304,6 +1332,17 @@
       <c r="E12" s="9" t="n">
         <v>8.345000000000001</v>
       </c>
+      <c r="F12" s="9" t="n">
+        <v>1826.19</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>-73.68000000000001</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>-4.0%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1332,14 +1371,14 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Job 236341: actual cost $2,277 → sold margin -31%</t>
+          <t>Job 236341: invoiced $1,733, actual cost $2,277 → margin -31%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Project ID#128013   —   SPOT RW-260629-131349  ·  iQuote #223408</t>
+          <t>Project ID#128013:   SPOT RW-260629-131349  ·  iQuote #223408</t>
         </is>
       </c>
     </row>
@@ -1363,6 +1402,17 @@
       <c r="E16" s="9" t="n">
         <v>5.018</v>
       </c>
+      <c r="F16" s="9" t="n">
+        <v>2452.48</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>182.21</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>+7.4%</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -1393,7 +1443,7 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>PKG153007274 DLN29676   —   SPOT RW-260629-132636  ·  iQuote #223389</t>
+          <t>PKG153007274 DLN29676:   SPOT RW-260629-132636  ·  iQuote #223389</t>
         </is>
       </c>
     </row>
@@ -1417,6 +1467,17 @@
       <c r="E20" s="9" t="n">
         <v>1.629</v>
       </c>
+      <c r="F20" s="9" t="n">
+        <v>4029.71</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>-1260.98</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>-31.3%</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1447,7 +1508,7 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>1748 Meijer PED Tasty Biscuits + Dentastix   —   SPOT RW-260629-133153  ·  iQuote #223378</t>
+          <t>1748 Meijer PED Tasty Biscuits + Dentastix:   SPOT RW-260629-133153  ·  iQuote #223378</t>
         </is>
       </c>
     </row>
@@ -1471,6 +1532,17 @@
       <c r="E24" s="9" t="n">
         <v>15.434</v>
       </c>
+      <c r="F24" s="9" t="n">
+        <v>3141.12</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>717.38</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>+22.8%</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -1492,6 +1564,17 @@
       <c r="E25" s="9" t="n">
         <v>10.571</v>
       </c>
+      <c r="F25" s="9" t="n">
+        <v>6181.41</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>-895.76</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>-14.5%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -1529,7 +1612,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>MPC - Meijer Iams   —   SPOT RW-260629-134103  ·  iQuote #223376  ·  BECAME A JOB</t>
+          <t>MPC - Meijer Iams:   SPOT RW-260629-134103  ·  iQuote #223376  ·  BECAME A JOB</t>
         </is>
       </c>
     </row>
@@ -1553,6 +1636,17 @@
       <c r="E30" s="9" t="n">
         <v>19.152</v>
       </c>
+      <c r="F30" s="9" t="n">
+        <v>1163.37</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>+23.5%</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -1574,6 +1668,17 @@
       <c r="E31" s="9" t="n">
         <v>13.86</v>
       </c>
+      <c r="F31" s="9" t="n">
+        <v>1970.75</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>108.24</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -1604,7 +1709,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Kent Displays Mailer &amp; Insert   —   SPOT RW-260706-094426  ·  iQuote #223488</t>
+          <t>Kent Displays Mailer &amp; Insert:   SPOT RW-260706-094426  ·  iQuote #223488</t>
         </is>
       </c>
     </row>
@@ -1628,110 +1733,88 @@
       <c r="E35" s="9" t="n">
         <v>6.51</v>
       </c>
+      <c r="F35" s="9" t="n">
+        <v>1548.37</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>404.53</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>+26.1%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Mailer - Digital Print outside AND inside, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 277" rule</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>1915.76</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>6.386</v>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 300</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>1952.9</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>1548.37</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>404.53</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>+26.1%</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Insert - Plain white 2 sides, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>No print · CAD Cut · 300" rule</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>1110.58</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>3.702</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Insert - White 2 sides, 100% coverage outside, Digital Print outside, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 300" rule</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>1856.56</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>6.189</v>
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    note: per-component; 4 inserts have no iQuote counterpart</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Insert - Plain kraft, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>No print · CAD Cut · 300" rule</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>1062.33</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>3.541</v>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Kent Displays Mailer &amp; Insert:   SPOT RW-260706-094426  ·  iQuote #223488</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Insert - Plain kraft with 100% coverage outside, Digital Print outside, CAD Cut</t>
+          <t xml:space="preserve">    Mailer - Digital Print outside AND inside, CAD Cut</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · 300" rule</t>
+          <t>Satin print · CAD Cut · 277" rule</t>
         </is>
       </c>
       <c r="C40" s="9" t="n">
         <v>300</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1800.69</v>
+        <v>1915.76</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>6.002</v>
+        <v>6.386</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>2031.1</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>-115.34</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>-5.7%</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1741,1158 +1824,1318 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1952.9</v>
+        <v>1915.76</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>1548.37</v>
+        <v>2031.1</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>404.53</v>
+        <v>-115.34</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>+26.1%</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>-5.7%</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    note: per-component; 4 inserts have no iQuote counterpart</t>
+          <t xml:space="preserve">    note: per-component</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Kent Displays Mailer &amp; Insert   —   SPOT RW-260706-094426  ·  iQuote #223488</t>
+          <t>48 Count Nacho Fiesta:   SPOT RW-260706-110912  ·  iQuote #223498</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Mailer - Digital Print outside only, CAD Cut</t>
+          <t xml:space="preserve">    Display Header</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · 277" rule</t>
+          <t>Gloss print · CAD Cut · 80" rule</t>
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1952.9</v>
+        <v>991.12</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>6.51</v>
+        <v>3.964</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>818.97</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>+21.0%</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Mailer - Digital Print outside AND inside, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 277" rule</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>1915.76</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>6.386</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Insert - Plain white 2 sides, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>No print · CAD Cut · 300" rule</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>1110.58</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>3.702</v>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 250</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>991.12</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>818.97</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>172.15</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>+21.0%</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Insert - White 2 sides, 100% coverage outside, Digital Print outside, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 300" rule</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>1856.56</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>6.189</v>
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>48 Count Nacho Fiesta:   SPOT RW-260706-110912  ·  iQuote #223498</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Insert - Plain kraft, CAD Cut</t>
+          <t xml:space="preserve">    Display Header</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>No print · CAD Cut · 300" rule</t>
+          <t>Gloss print · CAD Cut · 80" rule</t>
         </is>
       </c>
       <c r="C49" s="9" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1062.33</v>
+        <v>1208.46</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>3.541</v>
+        <v>3.453</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>958.6</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>249.86</v>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>+26.1%</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Insert - Plain kraft with 100% coverage outside, Digital Print outside, CAD Cut</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 300" rule</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>1800.69</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>6.002</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 300</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>1915.76</v>
-      </c>
-      <c r="F51" s="10" t="n">
-        <v>2031.1</v>
-      </c>
-      <c r="G51" s="10" t="n">
-        <v>-115.34</v>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>-5.7%</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 350</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>1208.46</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>958.6</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>249.86</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>+26.1%</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>48 Count Nacho Fiesta:   SPOT RW-260706-110912  ·  iQuote #223498</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Display Header</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · 80" rule</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1478.65</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>2.957</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>1168.02</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>310.63</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>+26.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 500</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>1478.65</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>1168.02</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>310.63</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>+26.6%</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>48 Count Nacho Fiesta:   SPOT RW-260706-110912  ·  iQuote #223498</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Display Header</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · 80" rule</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1565.74</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>2.088</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>1517.07</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 750</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>1565.74</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>1517.07</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    note: per-component</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>48 Count Nacho Fiesta   —   SPOT RW-260706-110912  ·  iQuote #223498</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Display Header</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 80" rule</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="D55" s="9" t="n">
-        <v>991.12</v>
-      </c>
-      <c r="E55" s="9" t="n">
-        <v>3.964</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>991.12</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>818.97</v>
-      </c>
-      <c r="G56" s="10" t="n">
-        <v>172.15</v>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>+21.0%</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>48 Count Nacho Fiesta   —   SPOT RW-260706-110912  ·  iQuote #223498</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Display Header</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 80" rule</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="n">
-        <v>350</v>
-      </c>
-      <c r="D59" s="9" t="n">
-        <v>1208.46</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>3.453</v>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 350</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>1208.46</v>
-      </c>
-      <c r="F60" s="10" t="n">
-        <v>958.6</v>
-      </c>
-      <c r="G60" s="10" t="n">
-        <v>249.86</v>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>+26.1%</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>C8(C9) 26 LP Meijer Elvive Floorstand - 129729:   SPOT RW-260709-132147  ·  iQuote #221998</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Shelves (3 versions)</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · Die Cut (Crest) · 384" rule</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>1575</v>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>12649.14</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>8.031000000000001</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>48 Count Nacho Fiesta   —   SPOT RW-260706-110912  ·  iQuote #223498</t>
-        </is>
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Inside Back Panel</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · Die Cut (Crest) · 464" rule</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>6550.19</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>12.477</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Display Header</t>
+          <t xml:space="preserve">    Left Hand Side</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · 80" rule</t>
+          <t>Satin print · Die Cut (Crest) · Hand Stripped · 479" rule</t>
         </is>
       </c>
       <c r="C63" s="9" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1478.65</v>
+        <v>3746.68</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2.957</v>
+        <v>7.137</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>5152.81</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>-1406.13</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>-27.3%</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="n">
-        <v>1478.65</v>
-      </c>
-      <c r="F64" s="10" t="n">
-        <v>1168.02</v>
-      </c>
-      <c r="G64" s="10" t="n">
-        <v>310.63</v>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>+26.6%</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Right Hand Side</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · Die Cut (Crest) · Hand Stripped · 479" rule</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>3746.68</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>7.137</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>5152.81</v>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>-1406.13</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>-27.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Base Panel</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · Hand Stripped · 285" rule</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>3828.61</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>7.293</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>4943.04</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>-1114.43</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>-22.5%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>48 Count Nacho Fiesta   —   SPOT RW-260706-110912  ·  iQuote #223498</t>
-        </is>
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Product Box - Machine Run, Glue In</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · Die Cut (Crest) · Glued (1 jt) · 367" rule</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>3860.43</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>7.353</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Display Header</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 80" rule</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>1565.74</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>2.088</v>
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 525 kit</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="n">
+        <v>34381.73</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>40873.15</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>-6491.42</v>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>-15.9%</t>
+        </is>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 750</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>1565.74</v>
-      </c>
-      <c r="F68" s="10" t="n">
-        <v>1517.07</v>
-      </c>
-      <c r="G68" s="10" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>+3.2%</t>
-        </is>
-      </c>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    note: Riser excluded (not in SPOT est)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>C8(C9) 26 LP Meijer Elvive Floorstand - 129729   —   SPOT RW-260709-132147  ·  iQuote #221998</t>
+          <t>Re-Frame Display - Walmart (HOT Prototype):   SPOT RW-260717-111921  ·  iQuote #223706</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Shelves (3 versions)</t>
+          <t xml:space="preserve">    Middle Base</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Satin print · Die Cut (Crest) · 384" rule</t>
+          <t>Satin print · CAD Cut · Hand Stripped · 958" rule</t>
         </is>
       </c>
       <c r="C71" s="9" t="n">
-        <v>1575</v>
+        <v>2</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>12649.14</v>
+        <v>490.26</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>8.031000000000001</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inside Back Panel</t>
+          <t xml:space="preserve">    Shelf</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · Die Cut (Crest) · 464" rule</t>
+          <t>Satin print · CAD Cut · 279" rule</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>525</v>
+        <v>8</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>6550.19</v>
+        <v>511.19</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>12.477</v>
+        <v>63.899</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>280.84</v>
+      </c>
+      <c r="G72" s="9" t="n">
+        <v>230.35</v>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>+82.0%</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Left Hand Side</t>
+          <t xml:space="preserve">    Columns</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Satin print · Die Cut (Crest) · Hand Stripped · 479" rule</t>
+          <t>Satin print · CAD Cut · Glued (1 jt) · 559" rule</t>
         </is>
       </c>
       <c r="C73" s="9" t="n">
-        <v>525</v>
+        <v>4</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3746.68</v>
+        <v>561.54</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>7.137</v>
+        <v>140.385</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>226.14</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>+67.4%</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Right Hand Side</t>
+          <t xml:space="preserve">    Base Tray</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Satin print · Die Cut (Crest) · Hand Stripped · 479" rule</t>
+          <t>Satin print · CAD Cut · 697" rule</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>525</v>
+        <v>2</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>3746.68</v>
+        <v>482.62</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>7.137</v>
+        <v>241.31</v>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>290.57</v>
+      </c>
+      <c r="G74" s="9" t="n">
+        <v>192.05</v>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>+66.1%</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Base Panel</t>
+          <t xml:space="preserve">    Header</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 285" rule</t>
+          <t>Satin print · CAD Cut · 135" rule</t>
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>525</v>
+        <v>2</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>3828.61</v>
+        <v>405.49</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>7.293</v>
+        <v>202.745</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>226.42</v>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>179.07</v>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>+79.1%</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Product Box - Machine Run, Glue In</t>
+          <t xml:space="preserve">    Display Tray</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Satin print · Die Cut (Crest) · Glued (1 jt) · 367" rule</t>
+          <t>Satin print · CAD Cut · 296" rule</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>525</v>
+        <v>2</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>3860.43</v>
+        <v>408.34</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>7.353</v>
+        <v>204.17</v>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>258.67</v>
+      </c>
+      <c r="G76" s="9" t="n">
+        <v>149.67</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>+57.9%</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 525 kit</t>
+          <t xml:space="preserve">    TOTAL @ qty 2/4/8 kit</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>34381.73</v>
+        <v>2859.44</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>40873.15</v>
+        <v>1803.46</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>-6491.42</v>
+        <v>1055.98</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>-15.9%</t>
-        </is>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    note: Riser excluded (not in SPOT est)</t>
+          <t>+58.6%</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>J63068 - Moen Lowes Prepacks (Project 7655):   SPOT RW-260720-082503  ·  iQuote #223583  ·  BECAME A JOB   [OUTLIER — see detailed workbook]</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Re-Frame Display - Walmart (HOT Prototype)   —   SPOT RW-260717-111921  ·  iQuote #223706</t>
-        </is>
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Header </t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 117" rule</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>918</v>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>3410.98</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>3.716</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Middle Base</t>
+          <t xml:space="preserve">    Header </t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 958" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 117" rule</t>
         </is>
       </c>
       <c r="C81" s="9" t="n">
-        <v>2</v>
+        <v>1750</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>490.26</v>
+        <v>5612.15</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>245.13</v>
+        <v>3.207</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Shelf</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 279" rule</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>511.19</v>
-      </c>
-      <c r="E82" s="9" t="n">
-        <v>63.899</v>
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 918+1750</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>9023.129999999999</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>16354.54</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>-7331.41</v>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>-44.8%</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Columns</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Glued (1 jt) · 559" rule</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D83" s="9" t="n">
-        <v>561.54</v>
-      </c>
-      <c r="E83" s="9" t="n">
-        <v>140.385</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Base Tray</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 697" rule</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D84" s="9" t="n">
-        <v>482.62</v>
-      </c>
-      <c r="E84" s="9" t="n">
-        <v>241.31</v>
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    note: SPOT: 1 comp x 2 qty; iQuote: 2 products 919+1751</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Header</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 135" rule</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" s="9" t="n">
-        <v>405.49</v>
-      </c>
-      <c r="E85" s="9" t="n">
-        <v>202.745</v>
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>TSC Holiday Iams Cat Mixed Full Pallet:   SPOT RW-260720-083107  ·  iQuote #223752</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Display Tray</t>
+          <t xml:space="preserve">    Corner Graphic</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · 296" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · Tape (Reinforced x1) · 136" rule</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>408.34</v>
+        <v>3418.16</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>204.17</v>
+        <v>5.697</v>
+      </c>
+      <c r="F86" s="9" t="n">
+        <v>2931.56</v>
+      </c>
+      <c r="G86" s="9" t="n">
+        <v>486.6</v>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>+16.6%</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 2/4/8 kit</t>
+          <t xml:space="preserve">    TOTAL @ qty 600</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>2859.44</v>
+        <v>3418.16</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>1803.46</v>
+        <v>2931.56</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>1055.98</v>
+        <v>486.6</v>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>+58.6%</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>+16.6%</t>
+        </is>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>J63068 - Moen Lowes Prepacks (Project 7655)   —   SPOT RW-260720-082503  ·  iQuote #223583  ·  BECAME A JOB   [OUTLIER — see detailed workbook]</t>
+          <t>3M Wall Repair Kit:   SPOT RW-260720-093753  ·  iQuote #221299</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Header </t>
+          <t xml:space="preserve">    Standard Wall Repair Kit Box</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 117" rule</t>
+          <t>Satin print · CAD Cut · Hand Stripped · 311" rule</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>918</v>
+        <v>300</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>3410.98</v>
+        <v>2277.38</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>3.716</v>
+        <v>7.591</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>1932.45</v>
+      </c>
+      <c r="G90" s="9" t="n">
+        <v>344.93</v>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>+17.8%</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Header </t>
+          <t xml:space="preserve">    Premium Wall Repair Kit Box</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 117" rule</t>
+          <t>Satin print · CAD Cut · Hand Stripped · 343" rule</t>
         </is>
       </c>
       <c r="C91" s="9" t="n">
-        <v>1750</v>
+        <v>30</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>5612.15</v>
+        <v>729.51</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>3.207</v>
+        <v>24.317</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>637.71</v>
+      </c>
+      <c r="G91" s="9" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>+14.4%</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 918+1750</t>
+          <t xml:space="preserve">    TOTAL @ qty 30/300 kit</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>9023.129999999999</v>
+        <v>3006.89</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>16354.54</v>
+        <v>2570.16</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>-7331.41</v>
+        <v>436.73</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>-44.8%</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
+          <t>+17.0%</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Trad Favorites:   SPOT RW-260720-112723  ·  iQuote #223707</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D/C Tray</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 140" rule</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>3661.24</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>2.816</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>5528.87</v>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>-1867.63</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>-33.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 1300</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>3661.24</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>5528.87</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>-1867.63</v>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>-33.8%</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    note: SPOT: 1 comp x 2 qty; iQuote: 2 products 919+1751</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>TSC Holiday Iams Cat Mixed Full Pallet   —   SPOT RW-260720-083107  ·  iQuote #223752</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Corner Graphic</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · Tape (Reinforced x1) · 136" rule</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="n">
-        <v>600</v>
-      </c>
-      <c r="D96" s="9" t="n">
-        <v>3418.16</v>
-      </c>
-      <c r="E96" s="9" t="n">
-        <v>5.697</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 600</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="n">
-        <v>3418.16</v>
-      </c>
-      <c r="F97" s="10" t="n">
-        <v>2931.56</v>
-      </c>
-      <c r="G97" s="10" t="n">
-        <v>486.6</v>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>+16.6%</t>
-        </is>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Vitamix 154042 POP - 2pc / 154727:   SPOT RW-260720-132349  ·  iQuote #223702</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>3M Wall Repair Kit   —   SPOT RW-260720-093753  ·  iQuote #221299</t>
-        </is>
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Vitamix POP Component 1 of 2</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 381" rule</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>3871.75</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>15.487</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Standard Wall Repair Kit Box</t>
+          <t xml:space="preserve">    Vitamix POP Component 2 of 2</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 311" rule</t>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 365" rule</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2277.38</v>
+        <v>3873.08</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>7.591</v>
+        <v>15.492</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Premium Wall Repair Kit Box</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 343" rule</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D101" s="9" t="n">
-        <v>729.51</v>
-      </c>
-      <c r="E101" s="9" t="n">
-        <v>24.317</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 30/300 kit</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="n">
-        <v>3006.89</v>
-      </c>
-      <c r="F102" s="10" t="n">
-        <v>2570.16</v>
-      </c>
-      <c r="G102" s="10" t="n">
-        <v>436.73</v>
-      </c>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>+17.0%</t>
-        </is>
-      </c>
-      <c r="I102" s="15" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 250</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="n">
+        <v>7744.83</v>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>9166.92</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>-1422.09</v>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>-15.5%</t>
+        </is>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Vitamix 154042 POP - 2pc / 154727:   SPOT RW-260720-132349  ·  iQuote #223702</t>
+        </is>
+      </c>
+    </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>Trad Favorites   —   SPOT RW-260720-112723  ·  iQuote #223707</t>
-        </is>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Vitamix POP Component 1 of 2</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 381" rule</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>6999.57</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>13.999</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D/C Tray</t>
+          <t xml:space="preserve">    Vitamix POP Component 2 of 2</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 140" rule</t>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 365" rule</t>
         </is>
       </c>
       <c r="C105" s="9" t="n">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>3661.24</v>
+        <v>7000.9</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>2.816</v>
+        <v>14.002</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 1300</t>
+          <t xml:space="preserve">    TOTAL @ qty 500</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>3661.24</v>
+        <v>14000.47</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>5528.87</v>
+        <v>14908.08</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>-1867.63</v>
+        <v>-907.61</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>-33.8%</t>
-        </is>
-      </c>
-      <c r="I106" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>-6.1%</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>Vitamix 154042 POP - 2pc / 154727   —   SPOT RW-260720-132349  ·  iQuote #223702</t>
+          <t>TR-10351 16x8.5x6:   SPOT RW-260720-133223  ·  iQuote #223701</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Vitamix POP Component 1 of 2</t>
+          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x6</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 381" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 376" rule</t>
         </is>
       </c>
       <c r="C109" s="9" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>3871.75</v>
+        <v>1969.15</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>15.487</v>
+        <v>19.692</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Vitamix POP Component 2 of 2</t>
+          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x3.25</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 365" rule</t>
+          <t>Gloss print · CAD Cut · 314" rule</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3873.08</v>
+        <v>1368.74</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>15.492</v>
+        <v>13.687</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
+          <t xml:space="preserve">    TOTAL @ qty 100</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>7744.83</v>
+        <v>3337.89</v>
       </c>
       <c r="F111" s="10" t="n">
-        <v>9166.92</v>
+        <v>3463.91</v>
       </c>
       <c r="G111" s="10" t="n">
-        <v>-1422.09</v>
+        <v>-126.02</v>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>-15.5%</t>
-        </is>
-      </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
+          <t>-3.6%</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>Vitamix 154042 POP - 2pc / 154727   —   SPOT RW-260720-132349  ·  iQuote #223702</t>
+          <t>TR-10351 16x8.5x6:   SPOT RW-260720-133223  ·  iQuote #223701</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Vitamix POP Component 1 of 2</t>
+          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x6</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 381" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 376" rule</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>6999.57</v>
+        <v>3251.33</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>13.999</v>
+        <v>16.257</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Vitamix POP Component 2 of 2</t>
+          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x3.25</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 365" rule</t>
+          <t>Gloss print · CAD Cut · 314" rule</t>
         </is>
       </c>
       <c r="C115" s="9" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>7000.9</v>
+        <v>1745.06</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>14.002</v>
+        <v>8.725</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL @ qty 200</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>14000.47</v>
+        <v>4996.39</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>14908.08</v>
+        <v>5894.43</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>-907.61</v>
+        <v>-898.04</v>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>-6.1%</t>
-        </is>
-      </c>
-      <c r="I116" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>-15.2%</t>
+        </is>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>TR-10351 16x8.5x6   —   SPOT RW-260720-133223  ·  iQuote #223701</t>
+          <t>TR-10351 16x8.5x6:   SPOT RW-260720-133223  ·  iQuote #223701</t>
         </is>
       </c>
     </row>
@@ -2908,13 +3151,13 @@
         </is>
       </c>
       <c r="C119" s="9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1969.15</v>
+        <v>1474.02</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>19.692</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="120">
@@ -2929,1880 +3172,2375 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1368.74</v>
+        <v>975.05</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>13.687</v>
+        <v>19.501</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 100</t>
+          <t xml:space="preserve">    TOTAL @ qty 50</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>3337.89</v>
+        <v>2449.07</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>3463.91</v>
+        <v>2142.17</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>-126.02</v>
+        <v>306.9</v>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>-3.6%</t>
-        </is>
-      </c>
-      <c r="I121" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>+14.3%</t>
+        </is>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>TR-10351 16x8.5x6   —   SPOT RW-260720-133223  ·  iQuote #223701</t>
+          <t>Schaeffler Vehicle Lifetime P-17-EC-K251 87X87X43-INA Schachtel TEST:   SPOT RW-260720-134257  ·  iQuote #223689</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x6</t>
+          <t xml:space="preserve">    Digital direct print folding-style carton</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 376" rule</t>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (3 jt)</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>3251.33</v>
+        <v>5753.95</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>16.257</v>
+        <v>8.220000000000001</v>
+      </c>
+      <c r="F124" s="9" t="n">
+        <v>4904.67</v>
+      </c>
+      <c r="G124" s="9" t="n">
+        <v>849.28</v>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>+17.3%</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x3.25</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 314" rule</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="D125" s="9" t="n">
-        <v>1745.06</v>
-      </c>
-      <c r="E125" s="9" t="n">
-        <v>8.725</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 200</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="n">
-        <v>4996.39</v>
-      </c>
-      <c r="F126" s="10" t="n">
-        <v>5894.43</v>
-      </c>
-      <c r="G126" s="10" t="n">
-        <v>-898.04</v>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>-15.2%</t>
-        </is>
-      </c>
-      <c r="I126" s="15" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 700</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="n">
+        <v>5753.95</v>
+      </c>
+      <c r="F125" s="10" t="n">
+        <v>4904.67</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>849.28</v>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>+17.3%</t>
+        </is>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Fatt Boyy Knife &amp; Tool - Folding Knife Pizza Box:   SPOT RW-260721-102108  ·  iQuote #223785</t>
+        </is>
+      </c>
+    </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>TR-10351 16x8.5x6   —   SPOT RW-260720-133223  ·  iQuote #223701</t>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Folding Knife Pizza Box</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · Hand Stripped · 111" rule</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1183.59</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>2.367</v>
+      </c>
+      <c r="F128" s="9" t="n">
+        <v>1003.06</v>
+      </c>
+      <c r="G128" s="9" t="n">
+        <v>180.53</v>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>+18.0%</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x6</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 376" rule</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="n">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 500</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="n">
+        <v>1183.59</v>
+      </c>
+      <c r="F129" s="10" t="n">
+        <v>1003.06</v>
+      </c>
+      <c r="G129" s="10" t="n">
+        <v>180.53</v>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>+18.0%</t>
+        </is>
+      </c>
+      <c r="I129" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>New Piston Kit:   SPOT RW-260721-135500  ·  iQuote #223597  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Front Tuck w/ Partition</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 422" rule</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>3176.43</v>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>12.706</v>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>2749.42</v>
+      </c>
+      <c r="G132" s="9" t="n">
+        <v>427.01</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>+15.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 250</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="n">
+        <v>3176.43</v>
+      </c>
+      <c r="F133" s="10" t="n">
+        <v>2749.42</v>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>427.01</v>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>+15.5%</t>
+        </is>
+      </c>
+      <c r="I133" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>Vitamix digital pricing for orders:   SPOT RW-260722-082345  ·  iQuote #223591  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RSC</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 504" rule</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>250</v>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>6773.57</v>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>27.094</v>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>6549.08</v>
+      </c>
+      <c r="G136" s="9" t="n">
+        <v>224.49</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>+3.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 250</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="n">
+        <v>6773.57</v>
+      </c>
+      <c r="F137" s="10" t="n">
+        <v>6549.08</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>224.49</v>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>+3.4%</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>Job 236943: invoiced $4,353, actual cost $9,468 → margin -118%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Vitamix digital pricing for orders:   SPOT RW-260722-082345  ·  iQuote #223591  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RSC</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 504" rule</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>8044.68</v>
+      </c>
+      <c r="E140" s="9" t="n">
+        <v>26.816</v>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>7577.35</v>
+      </c>
+      <c r="G140" s="9" t="n">
+        <v>467.33</v>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 300</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="n">
+        <v>8044.68</v>
+      </c>
+      <c r="F141" s="10" t="n">
+        <v>7577.35</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>467.33</v>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>RFQ Scotts 07-09-26:   SPOT RW-260722-085112  ·  iQuote #223596  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mini Pallet Band </t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · Die Cut (Crest) · Hand Stripped · 240" rule</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>4884.44</v>
+      </c>
+      <c r="E144" s="9" t="n">
+        <v>4.884</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mini Pallet Band</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · Die Cut (Crest) · Hand Stripped · 299" rule</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>3596.67</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>5.138</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 700/1000 kit</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>8481.110000000001</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>9299.35</v>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>-818.24</v>
+      </c>
+      <c r="H146" s="10" t="inlineStr">
+        <is>
+          <t>-8.8%</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>Vitamix Power Prep Mixer digital reorder:   SPOT RW-260722-090416  ·  iQuote #223590  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RSC</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · Glued (1 jt) · 410" rule</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D129" s="9" t="n">
-        <v>1474.02</v>
-      </c>
-      <c r="E129" s="9" t="n">
-        <v>29.48</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Front Tuck Mailer 16x8.5x3.25</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 314" rule</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D130" s="9" t="n">
-        <v>975.05</v>
-      </c>
-      <c r="E130" s="9" t="n">
-        <v>19.501</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="D149" s="9" t="n">
+        <v>1120.73</v>
+      </c>
+      <c r="E149" s="9" t="n">
+        <v>22.415</v>
+      </c>
+      <c r="F149" s="9" t="n">
+        <v>724.2</v>
+      </c>
+      <c r="G149" s="9" t="n">
+        <v>396.53</v>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>+54.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    TOTAL @ qty 50</t>
         </is>
       </c>
-      <c r="D131" s="10" t="n">
-        <v>2449.07</v>
-      </c>
-      <c r="F131" s="10" t="n">
-        <v>2142.17</v>
-      </c>
-      <c r="G131" s="10" t="n">
-        <v>306.9</v>
-      </c>
-      <c r="H131" s="10" t="inlineStr">
-        <is>
-          <t>+14.3%</t>
-        </is>
-      </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t>Schaeffler Vehicle Lifetime P-17-EC-K251 87X87X43-INA Schachtel TEST   —   SPOT RW-260720-134257  ·  iQuote #223689</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Digital direct print folding-style carton</t>
-        </is>
-      </c>
-      <c r="B134" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (3 jt)</t>
-        </is>
-      </c>
-      <c r="C134" s="9" t="n">
-        <v>700</v>
-      </c>
-      <c r="D134" s="9" t="n">
-        <v>5753.95</v>
-      </c>
-      <c r="E134" s="9" t="n">
-        <v>8.220000000000001</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 700</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="n">
-        <v>5753.95</v>
-      </c>
-      <c r="F135" s="10" t="n">
-        <v>4904.67</v>
-      </c>
-      <c r="G135" s="10" t="n">
-        <v>849.28</v>
-      </c>
-      <c r="H135" s="10" t="inlineStr">
-        <is>
-          <t>+17.3%</t>
-        </is>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>Fatt Boyy Knife &amp; Tool - Folding Knife Pizza Box   —   SPOT RW-260721-102108  ·  iQuote #223785</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Folding Knife Pizza Box</t>
-        </is>
-      </c>
-      <c r="B138" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 111" rule</t>
-        </is>
-      </c>
-      <c r="C138" s="9" t="n">
+      <c r="D150" s="10" t="n">
+        <v>1120.73</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>724.2</v>
+      </c>
+      <c r="G150" s="10" t="n">
+        <v>396.53</v>
+      </c>
+      <c r="H150" s="10" t="inlineStr">
+        <is>
+          <t>+54.8%</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>RW-260722-095152:   SPOT RW-260722-095152  ·  iQuote #223575  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Display Header</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · Hand Stripped · 69" rule</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="D138" s="9" t="n">
-        <v>1183.59</v>
-      </c>
-      <c r="E138" s="9" t="n">
-        <v>2.367</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="D153" s="9" t="n">
+        <v>1288.67</v>
+      </c>
+      <c r="E153" s="9" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="F153" s="9" t="n">
+        <v>985.09</v>
+      </c>
+      <c r="G153" s="9" t="n">
+        <v>303.58</v>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>+30.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">    TOTAL @ qty 500</t>
         </is>
       </c>
-      <c r="D139" s="10" t="n">
-        <v>1183.59</v>
-      </c>
-      <c r="F139" s="10" t="n">
-        <v>1003.06</v>
-      </c>
-      <c r="G139" s="10" t="n">
-        <v>180.53</v>
-      </c>
-      <c r="H139" s="10" t="inlineStr">
-        <is>
-          <t>+18.0%</t>
-        </is>
-      </c>
-      <c r="I139" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>New Piston Kit   —   SPOT RW-260721-135500  ·  iQuote #223597  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Front Tuck w/ Partition</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 422" rule</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="D142" s="9" t="n">
-        <v>3176.43</v>
-      </c>
-      <c r="E142" s="9" t="n">
-        <v>12.706</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="n">
-        <v>3176.43</v>
-      </c>
-      <c r="F143" s="10" t="n">
-        <v>2749.42</v>
-      </c>
-      <c r="G143" s="10" t="n">
-        <v>427.01</v>
-      </c>
-      <c r="H143" s="10" t="inlineStr">
-        <is>
-          <t>+15.5%</t>
-        </is>
-      </c>
-      <c r="I143" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>Vitamix digital pricing for orders   —   SPOT RW-260722-082345  ·  iQuote #223591  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RSC</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 504" rule</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="D146" s="9" t="n">
-        <v>6773.57</v>
-      </c>
-      <c r="E146" s="9" t="n">
-        <v>27.094</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="n">
-        <v>6773.57</v>
-      </c>
-      <c r="F147" s="10" t="n">
-        <v>6549.08</v>
-      </c>
-      <c r="G147" s="10" t="n">
-        <v>224.49</v>
-      </c>
-      <c r="H147" s="10" t="inlineStr">
-        <is>
-          <t>+3.4%</t>
-        </is>
-      </c>
-      <c r="I147" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J147" s="13" t="inlineStr">
-        <is>
-          <t>Job 236943: actual cost $9,468 → sold margin -118%</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>Vitamix digital pricing for orders   —   SPOT RW-260722-082345  ·  iQuote #223591  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RSC</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 504" rule</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D150" s="9" t="n">
-        <v>8044.68</v>
-      </c>
-      <c r="E150" s="9" t="n">
-        <v>26.816</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 300</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="n">
-        <v>8044.68</v>
-      </c>
-      <c r="F151" s="10" t="n">
-        <v>7577.35</v>
-      </c>
-      <c r="G151" s="10" t="n">
-        <v>467.33</v>
-      </c>
-      <c r="H151" s="10" t="inlineStr">
-        <is>
-          <t>+6.2%</t>
-        </is>
-      </c>
-      <c r="I151" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>RFQ Scotts 07-09-26   —   SPOT RW-260722-085112  ·  iQuote #223596  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Mini Pallet Band </t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · Die Cut (Crest) · Hand Stripped · 240" rule</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D154" s="9" t="n">
-        <v>4884.44</v>
-      </c>
-      <c r="E154" s="9" t="n">
-        <v>4.884</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Mini Pallet Band</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · Die Cut (Crest) · Hand Stripped · 299" rule</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="n">
-        <v>700</v>
-      </c>
-      <c r="D155" s="9" t="n">
-        <v>3596.67</v>
-      </c>
-      <c r="E155" s="9" t="n">
-        <v>5.138</v>
+      <c r="D154" s="10" t="n">
+        <v>1288.67</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>985.09</v>
+      </c>
+      <c r="G154" s="10" t="n">
+        <v>303.58</v>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>+30.8%</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 700/1000 kit</t>
-        </is>
-      </c>
-      <c r="D156" s="10" t="n">
-        <v>8481.110000000001</v>
-      </c>
-      <c r="F156" s="10" t="n">
-        <v>9299.35</v>
-      </c>
-      <c r="G156" s="10" t="n">
-        <v>-818.24</v>
-      </c>
-      <c r="H156" s="10" t="inlineStr">
-        <is>
-          <t>-8.8%</t>
-        </is>
-      </c>
-      <c r="I156" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Concept 100 Valentines Day Display:   SPOT RW-260723-084853  ·  iQuote #223791   [OUTLIER — see detailed workbook]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Back Panel</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 637" rule</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>944.3200000000001</v>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>62.955</v>
+      </c>
+      <c r="F157" s="9" t="n">
+        <v>787.65</v>
+      </c>
+      <c r="G157" s="9" t="n">
+        <v>156.67</v>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>+19.9%</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>Vitamix Power Prep Mixer digital reorder   —   SPOT RW-260722-090416  ·  iQuote #223590  ·  BECAME A JOB</t>
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Side Panel</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 941" rule</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>836.3099999999999</v>
+      </c>
+      <c r="E158" s="9" t="n">
+        <v>55.754</v>
+      </c>
+      <c r="F158" s="9" t="n">
+        <v>633.99</v>
+      </c>
+      <c r="G158" s="9" t="n">
+        <v>202.32</v>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>+31.9%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    RSC</t>
+          <t xml:space="preserve">    Angled Side Panel</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · Glued (1 jt) · 410" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 985" rule</t>
         </is>
       </c>
       <c r="C159" s="9" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1120.73</v>
+        <v>845.26</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>22.415</v>
+        <v>56.351</v>
+      </c>
+      <c r="F159" s="9" t="n">
+        <v>689.45</v>
+      </c>
+      <c r="G159" s="9" t="n">
+        <v>155.81</v>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>+22.6%</t>
+        </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
-        </is>
-      </c>
-      <c r="D160" s="10" t="n">
-        <v>1120.73</v>
-      </c>
-      <c r="F160" s="10" t="n">
-        <v>724.2</v>
-      </c>
-      <c r="G160" s="10" t="n">
-        <v>396.53</v>
-      </c>
-      <c r="H160" s="10" t="inlineStr">
-        <is>
-          <t>+54.8%</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Heart Middle Side 1</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 491" rule</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>938.51</v>
+      </c>
+      <c r="E160" s="9" t="n">
+        <v>62.567</v>
+      </c>
+      <c r="F160" s="9" t="n">
+        <v>564.36</v>
+      </c>
+      <c r="G160" s="9" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>+66.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Heart Middle Side 2</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 493" rule</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>938.76</v>
+      </c>
+      <c r="E161" s="9" t="n">
+        <v>62.584</v>
+      </c>
+      <c r="F161" s="9" t="n">
+        <v>564.54</v>
+      </c>
+      <c r="G161" s="9" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>+66.3%</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>RW-260722-095152   —   SPOT RW-260722-095152  ·  iQuote #223575  ·  BECAME A JOB</t>
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Shelf 1, 4 &amp; Big Heart Lug</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 650" rule</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>972.8099999999999</v>
+      </c>
+      <c r="E162" s="9" t="n">
+        <v>64.854</v>
+      </c>
+      <c r="F162" s="9" t="n">
+        <v>585.22</v>
+      </c>
+      <c r="G162" s="9" t="n">
+        <v>387.59</v>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>+66.2%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Display Header</t>
+          <t xml:space="preserve">    Shelves 3 &amp; 2</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 69" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 500" rule</t>
         </is>
       </c>
       <c r="C163" s="9" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1288.67</v>
+        <v>774.77</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>2.577</v>
+        <v>51.651</v>
+      </c>
+      <c r="F163" s="9" t="n">
+        <v>550.75</v>
+      </c>
+      <c r="G163" s="9" t="n">
+        <v>224.02</v>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>+40.7%</t>
+        </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
-        </is>
-      </c>
-      <c r="D164" s="10" t="n">
-        <v>1288.67</v>
-      </c>
-      <c r="F164" s="10" t="n">
-        <v>985.09</v>
-      </c>
-      <c r="G164" s="10" t="n">
-        <v>303.58</v>
-      </c>
-      <c r="H164" s="10" t="inlineStr">
-        <is>
-          <t>+30.8%</t>
-        </is>
-      </c>
-      <c r="I164" s="11" t="inlineStr">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Roll Up 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 687" rule</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>798.4299999999999</v>
+      </c>
+      <c r="E164" s="9" t="n">
+        <v>53.229</v>
+      </c>
+      <c r="F164" s="9" t="n">
+        <v>629.91</v>
+      </c>
+      <c r="G164" s="9" t="n">
+        <v>168.52</v>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>+26.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Bottom Shelf Eggcrate &amp; 4th Roll Up</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · Saber + D/C · Hand Stripped · 750" rule</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>7839.9</v>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>522.66</v>
+      </c>
+      <c r="F165" s="9" t="n">
+        <v>647.64</v>
+      </c>
+      <c r="G165" s="9" t="n">
+        <v>7192.26</v>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>+1110.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 15</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n">
+        <v>14889.07</v>
+      </c>
+      <c r="F166" s="10" t="n">
+        <v>5653.51</v>
+      </c>
+      <c r="G166" s="10" t="n">
+        <v>9235.559999999999</v>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t>+163.4%</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t>Concept 100 Valentines Day Display   —   SPOT RW-260723-084853  ·  iQuote #223791   [OUTLIER — see detailed workbook]</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Back Panel</t>
-        </is>
-      </c>
-      <c r="B167" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 637" rule</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D167" s="9" t="n">
-        <v>944.3200000000001</v>
-      </c>
-      <c r="E167" s="9" t="n">
-        <v>62.955</v>
-      </c>
-    </row>
     <row r="168">
-      <c r="A168" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Side Panel</t>
-        </is>
-      </c>
-      <c r="B168" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 941" rule</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D168" s="9" t="n">
-        <v>836.3099999999999</v>
-      </c>
-      <c r="E168" s="9" t="n">
-        <v>55.754</v>
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>Concept 100 Valentines Day Display:   SPOT RW-260723-084853  ·  iQuote #223791   [OUTLIER — see detailed workbook]</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Angled Side Panel</t>
+          <t xml:space="preserve">    Back Panel</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 985" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 637" rule</t>
         </is>
       </c>
       <c r="C169" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>845.26</v>
+        <v>714.33</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>56.351</v>
+        <v>89.291</v>
+      </c>
+      <c r="F169" s="9" t="n">
+        <v>631.99</v>
+      </c>
+      <c r="G169" s="9" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>+13.0%</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Heart Middle Side 1</t>
+          <t xml:space="preserve">    Side Panel</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 491" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 941" rule</t>
         </is>
       </c>
       <c r="C170" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D170" s="9" t="n">
-        <v>938.51</v>
+        <v>611.73</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>62.567</v>
+        <v>76.46599999999999</v>
+      </c>
+      <c r="F170" s="9" t="n">
+        <v>494.58</v>
+      </c>
+      <c r="G170" s="9" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>+23.7%</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Heart Middle Side 2</t>
+          <t xml:space="preserve">    Angled Side Panel</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 493" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 985" rule</t>
         </is>
       </c>
       <c r="C171" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>938.76</v>
+        <v>618.16</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>62.584</v>
+        <v>77.27</v>
+      </c>
+      <c r="F171" s="9" t="n">
+        <v>545.5599999999999</v>
+      </c>
+      <c r="G171" s="9" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>+13.3%</t>
+        </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Shelf 1, 4 &amp; Big Heart Lug</t>
+          <t xml:space="preserve">    Heart Middle Side 1</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 650" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 491" rule</t>
         </is>
       </c>
       <c r="C172" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D172" s="9" t="n">
-        <v>972.8099999999999</v>
+        <v>690.3200000000001</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>64.854</v>
+        <v>86.29000000000001</v>
+      </c>
+      <c r="F172" s="9" t="n">
+        <v>423.35</v>
+      </c>
+      <c r="G172" s="9" t="n">
+        <v>266.97</v>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>+63.1%</t>
+        </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Shelves 3 &amp; 2</t>
+          <t xml:space="preserve">    Heart Middle Side 2</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 500" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 493" rule</t>
         </is>
       </c>
       <c r="C173" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>774.77</v>
+        <v>690.45</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>51.651</v>
+        <v>86.306</v>
+      </c>
+      <c r="F173" s="9" t="n">
+        <v>423.45</v>
+      </c>
+      <c r="G173" s="9" t="n">
+        <v>267</v>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>+63.1%</t>
+        </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Roll Up 1 &amp; 2</t>
+          <t xml:space="preserve">    Shelf 1, 4 &amp; Big Heart Lug</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 687" rule</t>
+          <t>Gloss print · CAD Cut · Hand Stripped · 650" rule</t>
         </is>
       </c>
       <c r="C174" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D174" s="9" t="n">
-        <v>798.4299999999999</v>
+        <v>715.5</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>53.229</v>
+        <v>89.438</v>
+      </c>
+      <c r="F174" s="9" t="n">
+        <v>434.98</v>
+      </c>
+      <c r="G174" s="9" t="n">
+        <v>280.52</v>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>+64.5%</t>
+        </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Shelves 3 &amp; 2</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 500" rule</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>575.34</v>
+      </c>
+      <c r="E175" s="9" t="n">
+        <v>71.91800000000001</v>
+      </c>
+      <c r="F175" s="9" t="n">
+        <v>471.09</v>
+      </c>
+      <c r="G175" s="9" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>+22.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Roll Up 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 687" rule</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>588.34</v>
+      </c>
+      <c r="E176" s="9" t="n">
+        <v>73.54300000000001</v>
+      </c>
+      <c r="F176" s="9" t="n">
+        <v>513.35</v>
+      </c>
+      <c r="G176" s="9" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>+14.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Bottom Shelf Eggcrate &amp; 4th Roll Up</t>
         </is>
       </c>
-      <c r="B175" s="9" t="inlineStr">
+      <c r="B177" s="9" t="inlineStr">
         <is>
           <t>Gloss print · Saber + D/C · Hand Stripped · 750" rule</t>
         </is>
       </c>
-      <c r="C175" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D175" s="9" t="n">
-        <v>7839.9</v>
-      </c>
-      <c r="E175" s="9" t="n">
-        <v>522.66</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 15</t>
-        </is>
-      </c>
-      <c r="D176" s="10" t="n">
-        <v>14889.07</v>
-      </c>
-      <c r="F176" s="10" t="n">
-        <v>5653.51</v>
-      </c>
-      <c r="G176" s="10" t="n">
-        <v>9235.559999999999</v>
-      </c>
-      <c r="H176" s="10" t="inlineStr">
-        <is>
-          <t>+163.4%</t>
-        </is>
-      </c>
-      <c r="I176" s="11" t="inlineStr">
+      <c r="C177" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>9569.75</v>
+      </c>
+      <c r="E177" s="9" t="n">
+        <v>1196.219</v>
+      </c>
+      <c r="F177" s="9" t="n">
+        <v>523.29</v>
+      </c>
+      <c r="G177" s="9" t="n">
+        <v>9046.459999999999</v>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>+1728.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 8</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n">
+        <v>14773.92</v>
+      </c>
+      <c r="F178" s="10" t="n">
+        <v>4461.64</v>
+      </c>
+      <c r="G178" s="10" t="n">
+        <v>10312.28</v>
+      </c>
+      <c r="H178" s="10" t="inlineStr">
+        <is>
+          <t>+231.1%</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t>Concept 100 Valentines Day Display   —   SPOT RW-260723-084853  ·  iQuote #223791   [OUTLIER — see detailed workbook]</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Back Panel</t>
-        </is>
-      </c>
-      <c r="B179" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 637" rule</t>
-        </is>
-      </c>
-      <c r="C179" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D179" s="9" t="n">
-        <v>714.33</v>
-      </c>
-      <c r="E179" s="9" t="n">
-        <v>89.291</v>
-      </c>
-    </row>
     <row r="180">
-      <c r="A180" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Side Panel</t>
-        </is>
-      </c>
-      <c r="B180" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 941" rule</t>
-        </is>
-      </c>
-      <c r="C180" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D180" s="9" t="n">
-        <v>611.73</v>
-      </c>
-      <c r="E180" s="9" t="n">
-        <v>76.46599999999999</v>
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>0904-219 Center Joint:   SPOT RW-260724-113737  ·  iQuote #223651  ·  BECAME A JOB</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Angled Side Panel</t>
+          <t xml:space="preserve">    D/C Joined</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 985" rule</t>
+          <t>No print · CAD Cut · Hand Stripped · 123" rule</t>
         </is>
       </c>
       <c r="C181" s="9" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>618.16</v>
+        <v>132.39</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>77.27</v>
+        <v>6.018</v>
+      </c>
+      <c r="F181" s="9" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="G181" s="9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Heart Middle Side 1</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 491" rule</t>
-        </is>
-      </c>
-      <c r="C182" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D182" s="9" t="n">
-        <v>690.3200000000001</v>
-      </c>
-      <c r="E182" s="9" t="n">
-        <v>86.29000000000001</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Heart Middle Side 2</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 493" rule</t>
-        </is>
-      </c>
-      <c r="C183" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D183" s="9" t="n">
-        <v>690.45</v>
-      </c>
-      <c r="E183" s="9" t="n">
-        <v>86.306</v>
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 22</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>132.39</v>
+      </c>
+      <c r="F182" s="10" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="G182" s="10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H182" s="10" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="I182" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J182" s="13" t="inlineStr">
+        <is>
+          <t>Job 237252: invoiced $142, actual cost $164 → margin -15%</t>
+        </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Shelf 1, 4 &amp; Big Heart Lug</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 650" rule</t>
-        </is>
-      </c>
-      <c r="C184" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D184" s="9" t="n">
-        <v>715.5</v>
-      </c>
-      <c r="E184" s="9" t="n">
-        <v>89.438</v>
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>0904-219 Center Joint:   SPOT RW-260724-113737  ·  iQuote #223651  ·  BECAME A JOB</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Shelves 3 &amp; 2</t>
+          <t xml:space="preserve">    D/C Joined</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 500" rule</t>
+          <t>No print · CAD Cut · Hand Stripped · 123" rule</t>
         </is>
       </c>
       <c r="C185" s="9" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D185" s="9" t="n">
-        <v>575.34</v>
+        <v>194.89</v>
       </c>
       <c r="E185" s="9" t="n">
-        <v>71.91800000000001</v>
+        <v>3.303</v>
+      </c>
+      <c r="F185" s="9" t="n">
+        <v>157.17</v>
+      </c>
+      <c r="G185" s="9" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>+24.0%</t>
+        </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Roll Up 1 &amp; 2</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 687" rule</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D186" s="9" t="n">
-        <v>588.34</v>
-      </c>
-      <c r="E186" s="9" t="n">
-        <v>73.54300000000001</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Bottom Shelf Eggcrate &amp; 4th Roll Up</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · Saber + D/C · Hand Stripped · 750" rule</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D187" s="9" t="n">
-        <v>9569.75</v>
-      </c>
-      <c r="E187" s="9" t="n">
-        <v>1196.219</v>
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 59</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>194.89</v>
+      </c>
+      <c r="F186" s="10" t="n">
+        <v>157.17</v>
+      </c>
+      <c r="G186" s="10" t="n">
+        <v>37.72</v>
+      </c>
+      <c r="H186" s="10" t="inlineStr">
+        <is>
+          <t>+24.0%</t>
+        </is>
+      </c>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 8</t>
-        </is>
-      </c>
-      <c r="D188" s="10" t="n">
-        <v>14773.92</v>
-      </c>
-      <c r="F188" s="10" t="n">
-        <v>4461.64</v>
-      </c>
-      <c r="G188" s="10" t="n">
-        <v>10312.28</v>
-      </c>
-      <c r="H188" s="10" t="inlineStr">
-        <is>
-          <t>+231.1%</t>
-        </is>
-      </c>
-      <c r="I188" s="11" t="inlineStr">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>Mala Girl 3 Pak PDQ:   SPOT RW-260724-153643  ·  iQuote #223851</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tray</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · 412" rule</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1065.44</v>
+      </c>
+      <c r="E189" s="9" t="n">
+        <v>42.618</v>
+      </c>
+      <c r="F189" s="9" t="n">
+        <v>626.83</v>
+      </c>
+      <c r="G189" s="9" t="n">
+        <v>438.61</v>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>+70.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Platform Dividers Combo</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · Hand Stripped · 392" rule</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>840.46</v>
+      </c>
+      <c r="E190" s="9" t="n">
+        <v>33.618</v>
+      </c>
+      <c r="F190" s="9" t="n">
+        <v>452.82</v>
+      </c>
+      <c r="G190" s="9" t="n">
+        <v>387.64</v>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>+85.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 25</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="n">
+        <v>1905.9</v>
+      </c>
+      <c r="F191" s="10" t="n">
+        <v>1079.65</v>
+      </c>
+      <c r="G191" s="10" t="n">
+        <v>826.25</v>
+      </c>
+      <c r="H191" s="10" t="inlineStr">
+        <is>
+          <t>+76.5%</t>
+        </is>
+      </c>
+      <c r="I191" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="8" t="inlineStr">
-        <is>
-          <t>0904-219 Center Joint   —   SPOT RW-260724-113737  ·  iQuote #223651  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="9" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>ACE HARDWARE 42 GAL TRASH BIN (REV):   SPOT RW-260727-080830  ·  iQuote #223209  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RSC</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · Hand Stripped · Glued (1 jt)</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>453.63</v>
+      </c>
+      <c r="E194" s="9" t="n">
+        <v>453.63</v>
+      </c>
+      <c r="F194" s="9" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="G194" s="9" t="n">
+        <v>211.73</v>
+      </c>
+      <c r="H194" s="9" t="inlineStr">
+        <is>
+          <t>+87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 1</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="n">
+        <v>453.63</v>
+      </c>
+      <c r="F195" s="10" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>211.73</v>
+      </c>
+      <c r="H195" s="10" t="inlineStr">
+        <is>
+          <t>+87.5%</t>
+        </is>
+      </c>
+      <c r="I195" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J195" s="16" t="inlineStr">
+        <is>
+          <t>Job 236355: invoiced $242, actual cost $194 → margin +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>Power Prep Mixer 01.27.2025:   SPOT RW-260727-090826  ·  iQuote #223590  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RSC</t>
+        </is>
+      </c>
+      <c r="B198" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · Glued (1 jt) · 410" rule</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>1361.8</v>
+      </c>
+      <c r="E198" s="9" t="n">
+        <v>13.618</v>
+      </c>
+      <c r="F198" s="9" t="n">
+        <v>1230.77</v>
+      </c>
+      <c r="G198" s="9" t="n">
+        <v>131.03</v>
+      </c>
+      <c r="H198" s="9" t="inlineStr">
+        <is>
+          <t>+10.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 100</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="n">
+        <v>1361.8</v>
+      </c>
+      <c r="F199" s="10" t="n">
+        <v>1230.77</v>
+      </c>
+      <c r="G199" s="10" t="n">
+        <v>131.03</v>
+      </c>
+      <c r="H199" s="10" t="inlineStr">
+        <is>
+          <t>+10.6%</t>
+        </is>
+      </c>
+      <c r="I199" s="15" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>Power Prep Mixer 01.27.2025:   SPOT RW-260727-090826  ·  iQuote #223590  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RSC</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Hand Stripped · Glued (1 jt) · 410" rule</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D202" s="9" t="n">
+        <v>1050.73</v>
+      </c>
+      <c r="E202" s="9" t="n">
+        <v>21.015</v>
+      </c>
+      <c r="F202" s="9" t="n">
+        <v>724.2</v>
+      </c>
+      <c r="G202" s="9" t="n">
+        <v>326.53</v>
+      </c>
+      <c r="H202" s="9" t="inlineStr">
+        <is>
+          <t>+45.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 50</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="n">
+        <v>1050.73</v>
+      </c>
+      <c r="F203" s="10" t="n">
+        <v>724.2</v>
+      </c>
+      <c r="G203" s="10" t="n">
+        <v>326.53</v>
+      </c>
+      <c r="H203" s="10" t="inlineStr">
+        <is>
+          <t>+45.1%</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>Natures Bounty Tray &amp; Graphic Block - J58302:   SPOT RW-260727-093930  ·  iQuote #223538  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PDQ Tray</t>
+        </is>
+      </c>
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · Hand Stripped · 495" rule</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="n">
+        <v>350</v>
+      </c>
+      <c r="D206" s="9" t="n">
+        <v>3776.74</v>
+      </c>
+      <c r="E206" s="9" t="n">
+        <v>10.791</v>
+      </c>
+      <c r="F206" s="9" t="n">
+        <v>4645.82</v>
+      </c>
+      <c r="G206" s="9" t="n">
+        <v>-869.08</v>
+      </c>
+      <c r="H206" s="9" t="inlineStr">
+        <is>
+          <t>-18.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Graphic Block</t>
+        </is>
+      </c>
+      <c r="B207" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · 253" rule</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="n">
+        <v>350</v>
+      </c>
+      <c r="D207" s="9" t="n">
+        <v>2815.08</v>
+      </c>
+      <c r="E207" s="9" t="n">
+        <v>8.042999999999999</v>
+      </c>
+      <c r="F207" s="9" t="n">
+        <v>2120.92</v>
+      </c>
+      <c r="G207" s="9" t="n">
+        <v>694.16</v>
+      </c>
+      <c r="H207" s="9" t="inlineStr">
+        <is>
+          <t>+32.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 350</t>
+        </is>
+      </c>
+      <c r="D208" s="10" t="n">
+        <v>6591.82</v>
+      </c>
+      <c r="F208" s="10" t="n">
+        <v>6766.74</v>
+      </c>
+      <c r="G208" s="10" t="n">
+        <v>-174.92</v>
+      </c>
+      <c r="H208" s="10" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
+        </is>
+      </c>
+      <c r="I208" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>Z109871-1 / Mettler-Toledo:   SPOT RW-260727-095102  ·  iQuote #223486  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    D/C Joined</t>
         </is>
       </c>
-      <c r="B191" s="9" t="inlineStr">
-        <is>
-          <t>No print · CAD Cut · Hand Stripped · 123" rule</t>
-        </is>
-      </c>
-      <c r="C191" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="D191" s="9" t="n">
-        <v>132.39</v>
-      </c>
-      <c r="E191" s="9" t="n">
-        <v>6.018</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 22</t>
-        </is>
-      </c>
-      <c r="D192" s="10" t="n">
-        <v>132.39</v>
-      </c>
-      <c r="F192" s="10" t="n">
-        <v>130.54</v>
-      </c>
-      <c r="G192" s="10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H192" s="10" t="inlineStr">
-        <is>
-          <t>+1.4%</t>
-        </is>
-      </c>
-      <c r="I192" s="12" t="inlineStr">
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>No print · CAD Cut · Hand Stripped · 196" rule</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D211" s="9" t="n">
+        <v>255.63</v>
+      </c>
+      <c r="E211" s="9" t="n">
+        <v>5.113</v>
+      </c>
+      <c r="F211" s="9" t="n">
+        <v>248.28</v>
+      </c>
+      <c r="G211" s="9" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 50</t>
+        </is>
+      </c>
+      <c r="D212" s="10" t="n">
+        <v>255.63</v>
+      </c>
+      <c r="F212" s="10" t="n">
+        <v>248.28</v>
+      </c>
+      <c r="G212" s="10" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H212" s="10" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+      <c r="I212" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J192" s="13" t="inlineStr">
-        <is>
-          <t>Job 237252: actual cost $164 → sold margin -15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="8" t="inlineStr">
-        <is>
-          <t>0904-219 Center Joint   —   SPOT RW-260724-113737  ·  iQuote #223651  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    D/C Joined</t>
-        </is>
-      </c>
-      <c r="B195" s="9" t="inlineStr">
-        <is>
-          <t>No print · CAD Cut · Hand Stripped · 123" rule</t>
-        </is>
-      </c>
-      <c r="C195" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="D195" s="9" t="n">
-        <v>194.89</v>
-      </c>
-      <c r="E195" s="9" t="n">
-        <v>3.303</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 59</t>
-        </is>
-      </c>
-      <c r="D196" s="10" t="n">
-        <v>194.89</v>
-      </c>
-      <c r="F196" s="10" t="n">
-        <v>157.17</v>
-      </c>
-      <c r="G196" s="10" t="n">
-        <v>37.72</v>
-      </c>
-      <c r="H196" s="10" t="inlineStr">
-        <is>
-          <t>+24.0%</t>
-        </is>
-      </c>
-      <c r="I196" s="11" t="inlineStr">
+      <c r="J212" s="16" t="inlineStr">
+        <is>
+          <t>Job 236688: invoiced $248, actual cost $207 → margin +17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>8FT LED Tubes / 95053687:   SPOT RW-260727-101129  ·  iQuote #223454  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5PF</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 914" rule</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="n">
+        <v>220</v>
+      </c>
+      <c r="D215" s="9" t="n">
+        <v>5824.4</v>
+      </c>
+      <c r="E215" s="9" t="n">
+        <v>26.475</v>
+      </c>
+      <c r="F215" s="9" t="n">
+        <v>6164.32</v>
+      </c>
+      <c r="G215" s="9" t="n">
+        <v>-339.92</v>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 220</t>
+        </is>
+      </c>
+      <c r="D216" s="10" t="n">
+        <v>5824.4</v>
+      </c>
+      <c r="F216" s="10" t="n">
+        <v>6164.32</v>
+      </c>
+      <c r="G216" s="10" t="n">
+        <v>-339.92</v>
+      </c>
+      <c r="H216" s="10" t="inlineStr">
+        <is>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="I216" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J216" s="16" t="inlineStr">
+        <is>
+          <t>Job 236802: invoiced $6,164, actual cost $4,859 → margin +21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>Whirlpool Press Sheet:   SPOT RW-260727-102959  ·  iQuote #223393  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SC24-101</t>
+        </is>
+      </c>
+      <c r="B219" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="n">
+        <v>230</v>
+      </c>
+      <c r="D219" s="9" t="n">
+        <v>1753.9</v>
+      </c>
+      <c r="E219" s="9" t="n">
+        <v>7.626</v>
+      </c>
+      <c r="F219" s="9" t="n">
+        <v>1387.27</v>
+      </c>
+      <c r="G219" s="9" t="n">
+        <v>366.63</v>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>+26.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 230</t>
+        </is>
+      </c>
+      <c r="D220" s="10" t="n">
+        <v>1753.9</v>
+      </c>
+      <c r="F220" s="10" t="n">
+        <v>1387.27</v>
+      </c>
+      <c r="G220" s="10" t="n">
+        <v>366.63</v>
+      </c>
+      <c r="H220" s="10" t="inlineStr">
+        <is>
+          <t>+26.4%</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t>Mala Girl 3 Pak PDQ   —   SPOT RW-260724-153643  ·  iQuote #223851</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tray</t>
-        </is>
-      </c>
-      <c r="B199" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · 412" rule</t>
-        </is>
-      </c>
-      <c r="C199" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="D199" s="9" t="n">
-        <v>1065.44</v>
-      </c>
-      <c r="E199" s="9" t="n">
-        <v>42.618</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Platform Dividers Combo</t>
-        </is>
-      </c>
-      <c r="B200" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 392" rule</t>
-        </is>
-      </c>
-      <c r="C200" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="D200" s="9" t="n">
-        <v>840.46</v>
-      </c>
-      <c r="E200" s="9" t="n">
-        <v>33.618</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 25</t>
-        </is>
-      </c>
-      <c r="D201" s="10" t="n">
-        <v>1905.9</v>
-      </c>
-      <c r="F201" s="10" t="n">
-        <v>1079.65</v>
-      </c>
-      <c r="G201" s="10" t="n">
-        <v>826.25</v>
-      </c>
-      <c r="H201" s="10" t="inlineStr">
-        <is>
-          <t>+76.5%</t>
-        </is>
-      </c>
-      <c r="I201" s="11" t="inlineStr">
+      <c r="J220" s="13" t="inlineStr">
+        <is>
+          <t>Job 236550: invoiced $1,387, actual cost $1,631 → margin -18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>MPC - Meijer Iams:   SPOT RW-260727-105300  ·  iQuote #223376  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D26-0126 Header</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · 254" rule</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D223" s="9" t="n">
+        <v>1444.15</v>
+      </c>
+      <c r="E223" s="9" t="n">
+        <v>19.255</v>
+      </c>
+      <c r="F223" s="9" t="n">
+        <v>1163.37</v>
+      </c>
+      <c r="G223" s="9" t="n">
+        <v>280.78</v>
+      </c>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>+24.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D26-0131 Graphic Panel</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D224" s="9" t="n">
+        <v>2353.88</v>
+      </c>
+      <c r="E224" s="9" t="n">
+        <v>15.693</v>
+      </c>
+      <c r="F224" s="9" t="n">
+        <v>1970.75</v>
+      </c>
+      <c r="G224" s="9" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>+19.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 75/150 kit</t>
+        </is>
+      </c>
+      <c r="D225" s="10" t="n">
+        <v>3798.03</v>
+      </c>
+      <c r="F225" s="10" t="n">
+        <v>3134.12</v>
+      </c>
+      <c r="G225" s="10" t="n">
+        <v>663.91</v>
+      </c>
+      <c r="H225" s="10" t="inlineStr">
+        <is>
+          <t>+21.2%</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="8" t="inlineStr">
-        <is>
-          <t>ACE HARDWARE 42 GAL TRASH BIN (REV)   —   SPOT RW-260727-080830  ·  iQuote #223209  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RSC</t>
-        </is>
-      </c>
-      <c r="B204" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Hand Stripped · Glued (1 jt)</t>
-        </is>
-      </c>
-      <c r="C204" s="9" t="n">
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>ICM Distributing Company Header:   SPOT RW-260727-144121  ·  iQuote #223575  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Display Header</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>Satin print · CAD Cut · 69" rule</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D228" s="9" t="n">
+        <v>1259.41</v>
+      </c>
+      <c r="E228" s="9" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="F228" s="9" t="n">
+        <v>985.09</v>
+      </c>
+      <c r="G228" s="9" t="n">
+        <v>274.32</v>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>+27.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 500</t>
+        </is>
+      </c>
+      <c r="D229" s="10" t="n">
+        <v>1259.41</v>
+      </c>
+      <c r="F229" s="10" t="n">
+        <v>985.09</v>
+      </c>
+      <c r="G229" s="10" t="n">
+        <v>274.32</v>
+      </c>
+      <c r="H229" s="10" t="inlineStr">
+        <is>
+          <t>+27.8%</t>
+        </is>
+      </c>
+      <c r="I229" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J229" s="16" t="inlineStr">
+        <is>
+          <t>Job 236822: invoiced $985, actual cost $926 → margin +6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>L'Oreal C15 LP COS ZUS01644 Inserts:   SPOT RW-260730-115948  ·  iQuote #223880  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sheet Scored</t>
+        </is>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
+        <is>
+          <t>No print · CAD Cut · 19" rule</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D232" s="9" t="n">
+        <v>3416.08</v>
+      </c>
+      <c r="E232" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F232" s="9" t="n">
+        <v>2279.73</v>
+      </c>
+      <c r="G232" s="9" t="n">
+        <v>1136.35</v>
+      </c>
+      <c r="H232" s="9" t="inlineStr">
+        <is>
+          <t>+49.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 22000</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="n">
+        <v>3416.08</v>
+      </c>
+      <c r="F233" s="10" t="n">
+        <v>2279.73</v>
+      </c>
+      <c r="G233" s="10" t="n">
+        <v>1136.35</v>
+      </c>
+      <c r="H233" s="10" t="inlineStr">
+        <is>
+          <t>+49.8%</t>
+        </is>
+      </c>
+      <c r="I233" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>Cento Authentic Italian Header:   SPOT RW-260730-153734  ·  iQuote #223837  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Display Header</t>
+        </is>
+      </c>
+      <c r="B236" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="D236" s="9" t="n">
+        <v>1668.47</v>
+      </c>
+      <c r="E236" s="9" t="n">
+        <v>3.337</v>
+      </c>
+      <c r="F236" s="9" t="n">
+        <v>1221.28</v>
+      </c>
+      <c r="G236" s="9" t="n">
+        <v>447.19</v>
+      </c>
+      <c r="H236" s="9" t="inlineStr">
+        <is>
+          <t>+36.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL @ qty 500</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="n">
+        <v>1668.47</v>
+      </c>
+      <c r="F237" s="10" t="n">
+        <v>1221.28</v>
+      </c>
+      <c r="G237" s="10" t="n">
+        <v>447.19</v>
+      </c>
+      <c r="H237" s="10" t="inlineStr">
+        <is>
+          <t>+36.6%</t>
+        </is>
+      </c>
+      <c r="I237" s="11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>Case# 00011159 - REVISED - Targeted Pet Treats Shelf Display:   SPOT RW-260730-154720  ·  iQuote #223784  ·  BECAME A JOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Shelf Display Box — Blue (MRO42966 RevA)</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Glued (1 jt) · 318" rule</t>
+        </is>
+      </c>
+      <c r="C240" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D204" s="9" t="n">
-        <v>453.63</v>
-      </c>
-      <c r="E204" s="9" t="n">
-        <v>453.63</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 1</t>
-        </is>
-      </c>
-      <c r="D205" s="10" t="n">
-        <v>453.63</v>
-      </c>
-      <c r="F205" s="10" t="n">
-        <v>241.9</v>
-      </c>
-      <c r="G205" s="10" t="n">
-        <v>211.73</v>
-      </c>
-      <c r="H205" s="10" t="inlineStr">
-        <is>
-          <t>+87.5%</t>
-        </is>
-      </c>
-      <c r="I205" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J205" s="16" t="inlineStr">
-        <is>
-          <t>Job 236355: actual cost $194 → sold margin +20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="8" t="inlineStr">
-        <is>
-          <t>Power Prep Mixer 01.27.2025   —   SPOT RW-260727-090826  ·  iQuote #223590  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RSC</t>
-        </is>
-      </c>
-      <c r="B208" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · Glued (1 jt) · 410" rule</t>
-        </is>
-      </c>
-      <c r="C208" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="D208" s="9" t="n">
-        <v>1361.8</v>
-      </c>
-      <c r="E208" s="9" t="n">
-        <v>13.618</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 100</t>
-        </is>
-      </c>
-      <c r="D209" s="10" t="n">
-        <v>1361.8</v>
-      </c>
-      <c r="F209" s="10" t="n">
-        <v>1230.77</v>
-      </c>
-      <c r="G209" s="10" t="n">
-        <v>131.03</v>
-      </c>
-      <c r="H209" s="10" t="inlineStr">
-        <is>
-          <t>+10.6%</t>
-        </is>
-      </c>
-      <c r="I209" s="15" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="8" t="inlineStr">
-        <is>
-          <t>Power Prep Mixer 01.27.2025   —   SPOT RW-260727-090826  ·  iQuote #223590  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RSC</t>
-        </is>
-      </c>
-      <c r="B212" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Hand Stripped · Glued (1 jt) · 410" rule</t>
-        </is>
-      </c>
-      <c r="C212" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D212" s="9" t="n">
-        <v>1050.73</v>
-      </c>
-      <c r="E212" s="9" t="n">
-        <v>21.015</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
-        </is>
-      </c>
-      <c r="D213" s="10" t="n">
-        <v>1050.73</v>
-      </c>
-      <c r="F213" s="10" t="n">
-        <v>724.2</v>
-      </c>
-      <c r="G213" s="10" t="n">
-        <v>326.53</v>
-      </c>
-      <c r="H213" s="10" t="inlineStr">
-        <is>
-          <t>+45.1%</t>
-        </is>
-      </c>
-      <c r="I213" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="8" t="inlineStr">
-        <is>
-          <t>Natures Bounty Tray &amp; Graphic Block - J58302   —   SPOT RW-260727-093930  ·  iQuote #223538  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    PDQ Tray</t>
-        </is>
-      </c>
-      <c r="B216" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Hand Stripped · 495" rule</t>
-        </is>
-      </c>
-      <c r="C216" s="9" t="n">
-        <v>350</v>
-      </c>
-      <c r="D216" s="9" t="n">
-        <v>3776.74</v>
-      </c>
-      <c r="E216" s="9" t="n">
-        <v>10.791</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Graphic Block</t>
-        </is>
-      </c>
-      <c r="B217" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 253" rule</t>
-        </is>
-      </c>
-      <c r="C217" s="9" t="n">
-        <v>350</v>
-      </c>
-      <c r="D217" s="9" t="n">
-        <v>2815.08</v>
-      </c>
-      <c r="E217" s="9" t="n">
-        <v>8.042999999999999</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 350</t>
-        </is>
-      </c>
-      <c r="D218" s="10" t="n">
-        <v>6591.82</v>
-      </c>
-      <c r="F218" s="10" t="n">
-        <v>6766.74</v>
-      </c>
-      <c r="G218" s="10" t="n">
-        <v>-174.92</v>
-      </c>
-      <c r="H218" s="10" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
-      <c r="I218" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="8" t="inlineStr">
-        <is>
-          <t>Z109871-1 / Mettler-Toledo   —   SPOT RW-260727-095102  ·  iQuote #223486  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    D/C Joined</t>
-        </is>
-      </c>
-      <c r="B221" s="9" t="inlineStr">
-        <is>
-          <t>No print · CAD Cut · Hand Stripped · 196" rule</t>
-        </is>
-      </c>
-      <c r="C221" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="D221" s="9" t="n">
-        <v>255.63</v>
-      </c>
-      <c r="E221" s="9" t="n">
-        <v>5.113</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
-        </is>
-      </c>
-      <c r="D222" s="10" t="n">
-        <v>255.63</v>
-      </c>
-      <c r="F222" s="10" t="n">
-        <v>248.28</v>
-      </c>
-      <c r="G222" s="10" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="H222" s="10" t="inlineStr">
-        <is>
-          <t>+3.0%</t>
-        </is>
-      </c>
-      <c r="I222" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J222" s="16" t="inlineStr">
-        <is>
-          <t>Job 236688: actual cost $207 → sold margin +17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="8" t="inlineStr">
-        <is>
-          <t>8FT LED Tubes / 95053687   —   SPOT RW-260727-101129  ·  iQuote #223454  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    5PF</t>
-        </is>
-      </c>
-      <c r="B225" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · Die Cut (Crest) · Hand Stripped · Glued (1 jt) · 914" rule</t>
-        </is>
-      </c>
-      <c r="C225" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="D225" s="9" t="n">
-        <v>5824.4</v>
-      </c>
-      <c r="E225" s="9" t="n">
-        <v>26.475</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 220</t>
-        </is>
-      </c>
-      <c r="D226" s="10" t="n">
-        <v>5824.4</v>
-      </c>
-      <c r="F226" s="10" t="n">
-        <v>6164.32</v>
-      </c>
-      <c r="G226" s="10" t="n">
-        <v>-339.92</v>
-      </c>
-      <c r="H226" s="10" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="I226" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J226" s="16" t="inlineStr">
-        <is>
-          <t>Job 236802: actual cost $4,859 → sold margin +21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="8" t="inlineStr">
-        <is>
-          <t>Whirlpool Press Sheet   —   SPOT RW-260727-102959  ·  iQuote #223393  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SC24-101</t>
-        </is>
-      </c>
-      <c r="B229" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut</t>
-        </is>
-      </c>
-      <c r="C229" s="9" t="n">
-        <v>230</v>
-      </c>
-      <c r="D229" s="9" t="n">
-        <v>1753.9</v>
-      </c>
-      <c r="E229" s="9" t="n">
-        <v>7.626</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 230</t>
-        </is>
-      </c>
-      <c r="D230" s="10" t="n">
-        <v>1753.9</v>
-      </c>
-      <c r="F230" s="10" t="n">
-        <v>1387.27</v>
-      </c>
-      <c r="G230" s="10" t="n">
-        <v>366.63</v>
-      </c>
-      <c r="H230" s="10" t="inlineStr">
-        <is>
-          <t>+26.4%</t>
-        </is>
-      </c>
-      <c r="I230" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J230" s="13" t="inlineStr">
-        <is>
-          <t>Job 236550: actual cost $1,631 → sold margin -18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>MPC - Meijer Iams   —   SPOT RW-260727-105300  ·  iQuote #223376  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    D26-0126 Header</t>
-        </is>
-      </c>
-      <c r="B233" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 254" rule</t>
-        </is>
-      </c>
-      <c r="C233" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="D233" s="9" t="n">
-        <v>1444.15</v>
-      </c>
-      <c r="E233" s="9" t="n">
-        <v>19.255</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    D26-0131 Graphic Panel</t>
-        </is>
-      </c>
-      <c r="B234" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut</t>
-        </is>
-      </c>
-      <c r="C234" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="D234" s="9" t="n">
-        <v>2353.88</v>
-      </c>
-      <c r="E234" s="9" t="n">
-        <v>15.693</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 75/150 kit</t>
-        </is>
-      </c>
-      <c r="D235" s="10" t="n">
-        <v>3798.03</v>
-      </c>
-      <c r="F235" s="10" t="n">
-        <v>3134.12</v>
-      </c>
-      <c r="G235" s="10" t="n">
-        <v>663.91</v>
-      </c>
-      <c r="H235" s="10" t="inlineStr">
-        <is>
-          <t>+21.2%</t>
-        </is>
-      </c>
-      <c r="I235" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="8" t="inlineStr">
-        <is>
-          <t>ICM Distributing Company Header   —   SPOT RW-260727-144121  ·  iQuote #223575  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Display Header</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · 69" rule</t>
-        </is>
-      </c>
-      <c r="C238" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="D238" s="9" t="n">
-        <v>1259.41</v>
-      </c>
-      <c r="E238" s="9" t="n">
-        <v>2.519</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
-        </is>
-      </c>
-      <c r="D239" s="10" t="n">
-        <v>1259.41</v>
-      </c>
-      <c r="F239" s="10" t="n">
-        <v>985.09</v>
-      </c>
-      <c r="G239" s="10" t="n">
-        <v>274.32</v>
-      </c>
-      <c r="H239" s="10" t="inlineStr">
-        <is>
-          <t>+27.8%</t>
-        </is>
-      </c>
-      <c r="I239" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J239" s="16" t="inlineStr">
-        <is>
-          <t>Job 236822: actual cost $926 → sold margin +6%</t>
+      <c r="D240" s="9" t="n">
+        <v>438.44</v>
+      </c>
+      <c r="E240" s="9" t="n">
+        <v>438.44</v>
+      </c>
+      <c r="F240" s="9" t="n">
+        <v>185.27</v>
+      </c>
+      <c r="G240" s="9" t="n">
+        <v>253.17</v>
+      </c>
+      <c r="H240" s="9" t="inlineStr">
+        <is>
+          <t>+136.6%</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="8" t="inlineStr">
-        <is>
-          <t>L'Oreal C15 LP COS ZUS01644 Inserts   —   SPOT RW-260730-115948  ·  iQuote #223880  ·  BECAME A JOB</t>
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Shelf Display Box — Peach (MRO42966 RevA)</t>
+        </is>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>Gloss print · CAD Cut · Glued (1 jt) · 318" rule</t>
+        </is>
+      </c>
+      <c r="C241" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" s="9" t="n">
+        <v>438.44</v>
+      </c>
+      <c r="E241" s="9" t="n">
+        <v>438.44</v>
+      </c>
+      <c r="F241" s="9" t="n">
+        <v>185.27</v>
+      </c>
+      <c r="G241" s="9" t="n">
+        <v>253.17</v>
+      </c>
+      <c r="H241" s="9" t="inlineStr">
+        <is>
+          <t>+136.6%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Sheet Scored</t>
+          <t xml:space="preserve">    Shelf Display Box — Yellow (MRO42966 RevA)</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>No print · CAD Cut · 19" rule</t>
+          <t>Satin print · CAD Cut · Glued (1 jt) · 318" rule</t>
         </is>
       </c>
       <c r="C242" s="9" t="n">
-        <v>22000</v>
+        <v>1</v>
       </c>
       <c r="D242" s="9" t="n">
-        <v>3416.08</v>
+        <v>454.26</v>
       </c>
       <c r="E242" s="9" t="n">
-        <v>0.155</v>
+        <v>454.26</v>
+      </c>
+      <c r="F242" s="9" t="n">
+        <v>276.12</v>
+      </c>
+      <c r="G242" s="9" t="n">
+        <v>178.14</v>
+      </c>
+      <c r="H242" s="9" t="inlineStr">
+        <is>
+          <t>+64.5%</t>
+        </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 22000</t>
+          <t xml:space="preserve">    TOTAL @ qty 1</t>
         </is>
       </c>
       <c r="D243" s="10" t="n">
-        <v>3416.08</v>
+        <v>1331.14</v>
       </c>
       <c r="F243" s="10" t="n">
-        <v>2279.73</v>
+        <v>906.92</v>
       </c>
       <c r="G243" s="10" t="n">
-        <v>1136.35</v>
+        <v>424.22</v>
       </c>
       <c r="H243" s="10" t="inlineStr">
         <is>
-          <t>+49.8%</t>
+          <t>+46.8%</t>
         </is>
       </c>
       <c r="I243" s="11" t="inlineStr">
@@ -4814,264 +5552,125 @@
     <row r="245">
       <c r="A245" s="8" t="inlineStr">
         <is>
-          <t>Cento Authentic Italian Header   —   SPOT RW-260730-153734  ·  iQuote #223837  ·  BECAME A JOB</t>
+          <t>New Piston Kit:   SPOT RW-260730-155412  ·  iQuote #223597  ·  BECAME A JOB</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Display Header</t>
+          <t xml:space="preserve">    Front Tuck w/ Partition</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
         <is>
-          <t>Gloss print · CAD Cut</t>
+          <t>Gloss print · CAD Cut · 422" rule</t>
         </is>
       </c>
       <c r="C246" s="9" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="D246" s="9" t="n">
-        <v>1668.47</v>
+        <v>3071.43</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>3.337</v>
+        <v>12.286</v>
+      </c>
+      <c r="F246" s="9" t="n">
+        <v>2749.42</v>
+      </c>
+      <c r="G246" s="9" t="n">
+        <v>322.01</v>
+      </c>
+      <c r="H246" s="9" t="inlineStr">
+        <is>
+          <t>+11.7%</t>
+        </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL @ qty 250</t>
         </is>
       </c>
       <c r="D247" s="10" t="n">
-        <v>1668.47</v>
+        <v>3071.43</v>
       </c>
       <c r="F247" s="10" t="n">
-        <v>1221.28</v>
+        <v>2749.42</v>
       </c>
       <c r="G247" s="10" t="n">
-        <v>447.19</v>
+        <v>322.01</v>
       </c>
       <c r="H247" s="10" t="inlineStr">
         <is>
-          <t>+36.6%</t>
-        </is>
-      </c>
-      <c r="I247" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="8" t="inlineStr">
-        <is>
-          <t>Case# 00011159 - REVISED - Targeted Pet Treats Shelf Display   —   SPOT RW-260730-154720  ·  iQuote #223784  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Shelf Display Box — Blue (MRO42966 RevA)</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Glued (1 jt) · 318" rule</t>
-        </is>
-      </c>
-      <c r="C250" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D250" s="9" t="n">
-        <v>438.44</v>
-      </c>
-      <c r="E250" s="9" t="n">
-        <v>438.44</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Shelf Display Box — Peach (MRO42966 RevA)</t>
-        </is>
-      </c>
-      <c r="B251" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · Glued (1 jt) · 318" rule</t>
-        </is>
-      </c>
-      <c r="C251" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D251" s="9" t="n">
-        <v>438.44</v>
-      </c>
-      <c r="E251" s="9" t="n">
-        <v>438.44</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Shelf Display Box — Yellow (MRO42966 RevA)</t>
-        </is>
-      </c>
-      <c r="B252" s="9" t="inlineStr">
-        <is>
-          <t>Satin print · CAD Cut · Glued (1 jt) · 318" rule</t>
-        </is>
-      </c>
-      <c r="C252" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D252" s="9" t="n">
-        <v>454.26</v>
-      </c>
-      <c r="E252" s="9" t="n">
-        <v>454.26</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 1</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="n">
-        <v>1331.14</v>
-      </c>
-      <c r="F253" s="10" t="n">
-        <v>906.92</v>
-      </c>
-      <c r="G253" s="10" t="n">
-        <v>424.22</v>
-      </c>
-      <c r="H253" s="10" t="inlineStr">
-        <is>
-          <t>+46.8%</t>
-        </is>
-      </c>
-      <c r="I253" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="8" t="inlineStr">
-        <is>
-          <t>New Piston Kit   —   SPOT RW-260730-155412  ·  iQuote #223597  ·  BECAME A JOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Front Tuck w/ Partition</t>
-        </is>
-      </c>
-      <c r="B256" s="9" t="inlineStr">
-        <is>
-          <t>Gloss print · CAD Cut · 422" rule</t>
-        </is>
-      </c>
-      <c r="C256" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="D256" s="9" t="n">
-        <v>3071.43</v>
-      </c>
-      <c r="E256" s="9" t="n">
-        <v>12.286</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
-        </is>
-      </c>
-      <c r="D257" s="10" t="n">
-        <v>3071.43</v>
-      </c>
-      <c r="F257" s="10" t="n">
-        <v>2749.42</v>
-      </c>
-      <c r="G257" s="10" t="n">
-        <v>322.01</v>
-      </c>
-      <c r="H257" s="10" t="inlineStr">
-        <is>
           <t>+11.7%</t>
         </is>
       </c>
-      <c r="I257" s="15" t="inlineStr">
+      <c r="I247" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="J257" s="16" t="inlineStr">
-        <is>
-          <t>Job 236869: actual cost $2,580 → sold margin +10%</t>
+      <c r="J247" s="16" t="inlineStr">
+        <is>
+          <t>Job 236869: invoiced $2,876, actual cost $2,580 → margin +10%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A203:J203"/>
+    <mergeCell ref="A85:J85"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A194:J194"/>
-    <mergeCell ref="A141:J141"/>
-    <mergeCell ref="A224:J224"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A135:J135"/>
+    <mergeCell ref="A188:J188"/>
+    <mergeCell ref="A131:J131"/>
+    <mergeCell ref="A184:J184"/>
+    <mergeCell ref="A231:J231"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A190:J190"/>
+    <mergeCell ref="A180:J180"/>
+    <mergeCell ref="A210:J210"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A52:J52"/>
     <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A152:J152"/>
     <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A220:J220"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A211:J211"/>
-    <mergeCell ref="A249:J249"/>
+    <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A143:J143"/>
     <mergeCell ref="A245:J245"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A166:J166"/>
-    <mergeCell ref="A232:J232"/>
-    <mergeCell ref="A207:J207"/>
+    <mergeCell ref="A148:J148"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A222:J222"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A98:J98"/>
     <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A178:J178"/>
-    <mergeCell ref="A241:J241"/>
+    <mergeCell ref="A94:J94"/>
+    <mergeCell ref="A103:J103"/>
+    <mergeCell ref="A79:J79"/>
     <mergeCell ref="A123:J123"/>
-    <mergeCell ref="A228:J228"/>
+    <mergeCell ref="A168:J168"/>
+    <mergeCell ref="A197:J197"/>
     <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A153:J153"/>
-    <mergeCell ref="A162:J162"/>
-    <mergeCell ref="A237:J237"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A137:J137"/>
-    <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A227:J227"/>
+    <mergeCell ref="A218:J218"/>
+    <mergeCell ref="A205:J205"/>
     <mergeCell ref="A108:J108"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A255:J255"/>
-    <mergeCell ref="A99:J99"/>
-    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A193:J193"/>
     <mergeCell ref="A118:J118"/>
-    <mergeCell ref="A133:J133"/>
     <mergeCell ref="A89:J89"/>
-    <mergeCell ref="A198:J198"/>
-    <mergeCell ref="A149:J149"/>
-    <mergeCell ref="A145:J145"/>
-    <mergeCell ref="A158:J158"/>
-    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A214:J214"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A139:J139"/>
+    <mergeCell ref="A239:J239"/>
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A104:J104"/>
+    <mergeCell ref="A235:J235"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5093,29 +5692,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Price Comparison — 9 produced jobs</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>MIS Job</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Actual Invoice $</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>iQuote Sell $</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>SPOT Sell $</t>
         </is>
@@ -5266,22 +5865,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Actual $</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>SPOT est $</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>iQuote est $</t>
         </is>

--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -1120,7 +1120,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Grouped by SPOT project. All $ are SELL prices. Component-level iQuote prices auto-matched by product name + qty (blank = no confident 1:1 match; totals always compare). Δ% = SPOT vs iQuote (+ = SPOT higher).</t>
+          <t>Grouped by SPOT project. COMPONENT ROWS compare COST (SPOT total cost vs iQuote TotalActualCost). TOTAL rows compare SELL PRICE. iQuote components auto-matched by product name + qty (blank = no confident 1:1 match). Δ% = SPOT vs iQuote (+ = SPOT higher).</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>SPOT Sell $</t>
+          <t>SPOT $</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>SPOT Sell $/ea</t>
+          <t>SPOT $/ea</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>iQuote Sell $</t>
+          <t>iQuote $</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1198,20 +1198,20 @@
         <v>515</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2928.76</v>
+        <v>2065.18</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>5.687</v>
+        <v>4.01</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>5749.66</v>
+        <v>3797.68</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-2820.9</v>
+        <v>-1732.5</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-45.6%</t>
         </is>
       </c>
     </row>
@@ -1230,20 +1230,20 @@
         <v>515</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2287.59</v>
+        <v>1526.31</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4.442</v>
+        <v>2.964</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>2045.03</v>
+        <v>1468.7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>242.56</v>
+        <v>57.61</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>+3.9%</t>
         </is>
       </c>
     </row>
@@ -1262,27 +1262,27 @@
         <v>515</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>547.47</v>
+        <v>363.77</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>1.063</v>
+        <v>0.706</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>323.78</v>
+        <v>244.26</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>223.69</v>
+        <v>119.51</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>+69.1%</t>
+          <t>+48.9%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 515</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 515</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
@@ -1327,27 +1327,27 @@
         <v>210</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1752.51</v>
+        <v>1122.58</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>8.345000000000001</v>
+        <v>5.346</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1826.19</v>
+        <v>1537.62</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>-73.68000000000001</v>
+        <v>-415.04</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-27.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 210</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 210</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
@@ -1397,27 +1397,27 @@
         <v>525</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2634.69</v>
+        <v>1745.07</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5.018</v>
+        <v>3.324</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2452.48</v>
+        <v>1670.62</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>182.21</v>
+        <v>74.45</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+4.5%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 525</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 525</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
@@ -1462,27 +1462,27 @@
         <v>1700</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2768.73</v>
+        <v>1913.13</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1.629</v>
+        <v>1.125</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>4029.71</v>
+        <v>3245.03</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>-1260.98</v>
+        <v>-1331.9</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-41.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 1700</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 1700</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
@@ -1527,20 +1527,20 @@
         <v>250</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>3858.5</v>
+        <v>2851.94</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>15.434</v>
+        <v>11.408</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>3141.12</v>
+        <v>2070.96</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>717.38</v>
+        <v>780.98</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>+22.8%</t>
+          <t>+37.7%</t>
         </is>
       </c>
     </row>
@@ -1559,27 +1559,27 @@
         <v>500</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>5285.65</v>
+        <v>3890.92</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10.571</v>
+        <v>7.782</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>6181.41</v>
+        <v>4068.04</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>-895.76</v>
+        <v>-177.12</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250 sets</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 250 sets</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
@@ -1631,20 +1631,20 @@
         <v>75</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1436.41</v>
+        <v>949.34</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>19.152</v>
+        <v>12.658</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1163.37</v>
+        <v>766.88</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>273.04</v>
+        <v>182.46</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>+23.5%</t>
+          <t>+23.8%</t>
         </is>
       </c>
     </row>
@@ -1663,27 +1663,27 @@
         <v>150</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2078.99</v>
+        <v>1358.05</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>13.86</v>
+        <v>9.054</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1970.75</v>
+        <v>1303.63</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>108.24</v>
+        <v>54.42</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+4.2%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 75/150 kit</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 75/150 kit</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
@@ -1728,27 +1728,27 @@
         <v>300</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>1952.9</v>
+        <v>1376.32</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6.51</v>
+        <v>4.588</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1548.37</v>
+        <v>1096.04</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>404.53</v>
+        <v>280.28</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>+26.1%</t>
+          <t>+25.6%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 300</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 300</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
@@ -1800,27 +1800,27 @@
         <v>300</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1915.76</v>
+        <v>1225.43</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>6.386</v>
+        <v>4.085</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>2031.1</v>
+        <v>1384.5</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>-115.34</v>
+        <v>-159.07</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-11.5%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 300</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 300</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
@@ -1872,27 +1872,27 @@
         <v>250</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>991.12</v>
+        <v>614.54</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>3.964</v>
+        <v>2.458</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>818.97</v>
+        <v>582.01</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>172.15</v>
+        <v>32.53</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>+21.0%</t>
+          <t>+5.6%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 250</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
@@ -1937,27 +1937,27 @@
         <v>350</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1208.46</v>
+        <v>723.21</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>3.453</v>
+        <v>2.066</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>958.6</v>
+        <v>678.4299999999999</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>249.86</v>
+        <v>44.78</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>+26.1%</t>
+          <t>+6.6%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 350</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 350</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
@@ -2002,27 +2002,27 @@
         <v>500</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1478.65</v>
+        <v>858.3</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>2.957</v>
+        <v>1.717</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>1168.02</v>
+        <v>823.05</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>310.63</v>
+        <v>35.25</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>+26.6%</t>
+          <t>+4.3%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 500</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
@@ -2067,27 +2067,27 @@
         <v>750</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1565.74</v>
+        <v>1074.46</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>2.088</v>
+        <v>1.433</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1517.07</v>
+        <v>1064.09</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>48.67</v>
+        <v>10.37</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+1.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 750</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 750</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
@@ -2132,10 +2132,10 @@
         <v>1575</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>12649.14</v>
+        <v>9499.35</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>8.031000000000001</v>
+        <v>6.031</v>
       </c>
     </row>
     <row r="62">
@@ -2153,10 +2153,10 @@
         <v>525</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>6550.19</v>
+        <v>4925.14</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>12.477</v>
+        <v>9.381</v>
       </c>
     </row>
     <row r="63">
@@ -2174,20 +2174,20 @@
         <v>525</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3746.68</v>
+        <v>2748.58</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>7.137</v>
+        <v>5.235</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>5152.81</v>
+        <v>3742.37</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>-1406.13</v>
+        <v>-993.79</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-26.6%</t>
         </is>
       </c>
     </row>
@@ -2206,20 +2206,20 @@
         <v>525</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>3746.68</v>
+        <v>2748.58</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>7.137</v>
+        <v>5.235</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>5152.81</v>
+        <v>3742.37</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>-1406.13</v>
+        <v>-993.79</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-26.6%</t>
         </is>
       </c>
     </row>
@@ -2238,20 +2238,20 @@
         <v>525</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>3828.61</v>
+        <v>2619.45</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>7.293</v>
+        <v>4.989</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>4943.04</v>
+        <v>3479.43</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>-1114.43</v>
+        <v>-859.98</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
@@ -2270,16 +2270,16 @@
         <v>525</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>3860.43</v>
+        <v>2831.61</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>7.353</v>
+        <v>5.394</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 525 kit</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 525 kit</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
@@ -2331,10 +2331,10 @@
         <v>2</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>490.26</v>
+        <v>317.63</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>245.13</v>
+        <v>158.815</v>
       </c>
     </row>
     <row r="72">
@@ -2352,20 +2352,20 @@
         <v>8</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>511.19</v>
+        <v>328.1</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>63.899</v>
+        <v>41.013</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>280.84</v>
+        <v>209.83</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>230.35</v>
+        <v>118.27</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>+82.0%</t>
+          <t>+56.4%</t>
         </is>
       </c>
     </row>
@@ -2384,20 +2384,20 @@
         <v>4</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>561.54</v>
+        <v>360.4</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>140.385</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>335.4</v>
+        <v>253.56</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>226.14</v>
+        <v>106.84</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>+67.4%</t>
+          <t>+42.1%</t>
         </is>
       </c>
     </row>
@@ -2416,20 +2416,20 @@
         <v>2</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>482.62</v>
+        <v>313.81</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>241.31</v>
+        <v>156.905</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>290.57</v>
+        <v>217.98</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>192.05</v>
+        <v>95.83</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>+66.1%</t>
+          <t>+44.0%</t>
         </is>
       </c>
     </row>
@@ -2448,20 +2448,20 @@
         <v>2</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>405.49</v>
+        <v>275.25</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>202.745</v>
+        <v>137.625</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>226.42</v>
+        <v>164.97</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>179.07</v>
+        <v>110.28</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>+79.1%</t>
+          <t>+66.8%</t>
         </is>
       </c>
     </row>
@@ -2480,27 +2480,27 @@
         <v>2</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>408.34</v>
+        <v>276.67</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>204.17</v>
+        <v>138.335</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>258.67</v>
+        <v>192.39</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>149.67</v>
+        <v>84.28</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>+57.9%</t>
+          <t>+43.8%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 2/4/8 kit</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 2/4/8 kit</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
@@ -2545,10 +2545,10 @@
         <v>918</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>3410.98</v>
+        <v>2333.29</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>3.716</v>
+        <v>2.542</v>
       </c>
     </row>
     <row r="81">
@@ -2566,16 +2566,16 @@
         <v>1750</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5612.15</v>
+        <v>4029.25</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>3.207</v>
+        <v>2.302</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 918+1750</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 918+1750</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
@@ -2627,27 +2627,27 @@
         <v>600</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>3418.16</v>
+        <v>2340.35</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>5.697</v>
+        <v>3.901</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>2931.56</v>
+        <v>1988.75</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>486.6</v>
+        <v>351.6</v>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>+16.6%</t>
+          <t>+17.7%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 600</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 600</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
@@ -2692,20 +2692,20 @@
         <v>300</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2277.38</v>
+        <v>1453.25</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>7.591</v>
+        <v>4.844</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>1932.45</v>
+        <v>1259.91</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>344.93</v>
+        <v>193.34</v>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+15.3%</t>
         </is>
       </c>
     </row>
@@ -2724,27 +2724,27 @@
         <v>30</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>729.51</v>
+        <v>389.75</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>24.317</v>
+        <v>12.992</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>637.71</v>
+        <v>395.56</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>91.8</v>
+        <v>-5.81</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 30/300 kit</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 30/300 kit</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
@@ -2789,27 +2789,27 @@
         <v>1300</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>3661.24</v>
+        <v>2686.21</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>2.816</v>
+        <v>2.066</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>5528.87</v>
+        <v>3634.81</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>-1867.63</v>
+        <v>-948.6</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-26.1%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 1300</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 1300</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
@@ -2854,10 +2854,10 @@
         <v>250</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>3871.75</v>
+        <v>2833.71</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>15.487</v>
+        <v>11.335</v>
       </c>
     </row>
     <row r="100">
@@ -2875,16 +2875,16 @@
         <v>250</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>3873.08</v>
+        <v>2833.71</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>15.492</v>
+        <v>11.335</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 250</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
@@ -2929,10 +2929,10 @@
         <v>500</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>6999.57</v>
+        <v>5253.93</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>13.999</v>
+        <v>10.508</v>
       </c>
     </row>
     <row r="105">
@@ -2950,16 +2950,16 @@
         <v>500</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>7000.9</v>
+        <v>5253.93</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>14.002</v>
+        <v>10.508</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 500</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
@@ -3004,10 +3004,10 @@
         <v>100</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1969.15</v>
+        <v>1283.18</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>19.692</v>
+        <v>12.832</v>
       </c>
     </row>
     <row r="110">
@@ -3025,16 +3025,16 @@
         <v>100</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1368.74</v>
+        <v>751.9299999999999</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>13.687</v>
+        <v>7.519</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 100</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 100</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
@@ -3079,10 +3079,10 @@
         <v>200</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>3251.33</v>
+        <v>2233.83</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>16.257</v>
+        <v>11.169</v>
       </c>
     </row>
     <row r="115">
@@ -3100,16 +3100,16 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1745.06</v>
+        <v>1141.07</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>8.725</v>
+        <v>5.705</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 200</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 200</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
@@ -3154,10 +3154,10 @@
         <v>50</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1474.02</v>
+        <v>805.13</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>29.48</v>
+        <v>16.103</v>
       </c>
     </row>
     <row r="120">
@@ -3175,16 +3175,16 @@
         <v>50</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>975.05</v>
+        <v>557.36</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>19.501</v>
+        <v>11.147</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 50</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
@@ -3229,27 +3229,27 @@
         <v>700</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>5753.95</v>
+        <v>4262.3</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>8.220000000000001</v>
+        <v>6.089</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>4904.67</v>
+        <v>3689.77</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>849.28</v>
+        <v>572.53</v>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>+17.3%</t>
+          <t>+15.5%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 700</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 700</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
@@ -3294,27 +3294,27 @@
         <v>500</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1183.59</v>
+        <v>651.79</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>2.367</v>
+        <v>1.304</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>1003.06</v>
+        <v>795.49</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>180.53</v>
+        <v>-143.7</v>
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 500</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
@@ -3359,27 +3359,27 @@
         <v>250</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>3176.43</v>
+        <v>2206.38</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>12.706</v>
+        <v>8.826000000000001</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>2749.42</v>
+        <v>1689.98</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>427.01</v>
+        <v>516.4</v>
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>+15.5%</t>
+          <t>+30.6%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 250</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
@@ -3424,27 +3424,27 @@
         <v>250</v>
       </c>
       <c r="D136" s="9" t="n">
-        <v>6773.57</v>
+        <v>5110.18</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>27.094</v>
+        <v>20.441</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>6549.08</v>
+        <v>4548.46</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>224.49</v>
+        <v>561.72</v>
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+12.3%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 250</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
@@ -3494,27 +3494,27 @@
         <v>300</v>
       </c>
       <c r="D140" s="9" t="n">
-        <v>8044.68</v>
+        <v>6063.51</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>26.816</v>
+        <v>20.212</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>7577.35</v>
+        <v>5237.31</v>
       </c>
       <c r="G140" s="9" t="n">
-        <v>467.33</v>
+        <v>826.2</v>
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+15.8%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 300</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 300</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
@@ -3559,10 +3559,10 @@
         <v>1000</v>
       </c>
       <c r="D144" s="9" t="n">
-        <v>4884.44</v>
+        <v>3529.3</v>
       </c>
       <c r="E144" s="9" t="n">
-        <v>4.884</v>
+        <v>3.529</v>
       </c>
     </row>
     <row r="145">
@@ -3580,16 +3580,16 @@
         <v>700</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3596.67</v>
+        <v>2612.82</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>5.138</v>
+        <v>3.733</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 700/1000 kit</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 700/1000 kit</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
@@ -3634,27 +3634,27 @@
         <v>50</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1120.73</v>
+        <v>620.37</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>22.415</v>
+        <v>12.407</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>724.2</v>
+        <v>573.99</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>396.53</v>
+        <v>46.38</v>
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>+54.8%</t>
+          <t>+8.1%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 50</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
@@ -3699,27 +3699,27 @@
         <v>500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1288.67</v>
+        <v>716.83</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>2.577</v>
+        <v>1.434</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>985.09</v>
+        <v>633.62</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>303.58</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>+30.8%</t>
+          <t>+13.1%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 500</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
@@ -3764,20 +3764,20 @@
         <v>15</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>944.3200000000001</v>
+        <v>497.02</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>62.955</v>
+        <v>33.135</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>787.65</v>
+        <v>521.58</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>156.67</v>
+        <v>-24.56</v>
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>+19.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
     </row>
@@ -3796,20 +3796,20 @@
         <v>15</v>
       </c>
       <c r="D158" s="9" t="n">
-        <v>836.3099999999999</v>
+        <v>443.01</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>55.754</v>
+        <v>29.534</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>633.99</v>
+        <v>440.72</v>
       </c>
       <c r="G158" s="9" t="n">
-        <v>202.32</v>
+        <v>2.29</v>
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>+31.9%</t>
+          <t>+0.5%</t>
         </is>
       </c>
     </row>
@@ -3828,20 +3828,20 @@
         <v>15</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>845.26</v>
+        <v>447.48</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>56.351</v>
+        <v>29.832</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>689.45</v>
+        <v>482.56</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>155.81</v>
+        <v>-35.08</v>
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>+22.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
     </row>
@@ -3860,20 +3860,20 @@
         <v>15</v>
       </c>
       <c r="D160" s="9" t="n">
-        <v>938.51</v>
+        <v>494.09</v>
       </c>
       <c r="E160" s="9" t="n">
-        <v>62.567</v>
+        <v>32.939</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>564.36</v>
+        <v>382.29</v>
       </c>
       <c r="G160" s="9" t="n">
-        <v>374.15</v>
+        <v>111.8</v>
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>+66.3%</t>
+          <t>+29.2%</t>
         </is>
       </c>
     </row>
@@ -3892,20 +3892,20 @@
         <v>15</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>938.76</v>
+        <v>494.21</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>62.584</v>
+        <v>32.947</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>564.54</v>
+        <v>382.43</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>374.22</v>
+        <v>111.78</v>
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
-          <t>+66.3%</t>
+          <t>+29.2%</t>
         </is>
       </c>
     </row>
@@ -3924,20 +3924,20 @@
         <v>15</v>
       </c>
       <c r="D162" s="9" t="n">
-        <v>972.8099999999999</v>
+        <v>511.21</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>64.854</v>
+        <v>34.081</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>585.22</v>
+        <v>398.61</v>
       </c>
       <c r="G162" s="9" t="n">
-        <v>387.59</v>
+        <v>112.6</v>
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
-          <t>+66.2%</t>
+          <t>+28.2%</t>
         </is>
       </c>
     </row>
@@ -3956,20 +3956,20 @@
         <v>15</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>774.77</v>
+        <v>412.25</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>51.651</v>
+        <v>27.483</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>550.75</v>
+        <v>372.16</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>224.02</v>
+        <v>40.09</v>
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
-          <t>+40.7%</t>
+          <t>+10.8%</t>
         </is>
       </c>
     </row>
@@ -3988,20 +3988,20 @@
         <v>15</v>
       </c>
       <c r="D164" s="9" t="n">
-        <v>798.4299999999999</v>
+        <v>424.08</v>
       </c>
       <c r="E164" s="9" t="n">
-        <v>53.229</v>
+        <v>28.272</v>
       </c>
       <c r="F164" s="9" t="n">
-        <v>629.91</v>
+        <v>435.33</v>
       </c>
       <c r="G164" s="9" t="n">
-        <v>168.52</v>
+        <v>-11.25</v>
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>+26.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
@@ -4020,27 +4020,27 @@
         <v>15</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>7839.9</v>
+        <v>5871.75</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>522.66</v>
+        <v>391.45</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>647.64</v>
+        <v>449.16</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>7192.26</v>
+        <v>5422.59</v>
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
-          <t>+1110.5%</t>
+          <t>+1207.3%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 15</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 15</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
@@ -4085,20 +4085,20 @@
         <v>8</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>714.33</v>
+        <v>382.16</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>89.291</v>
+        <v>47.77</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>631.99</v>
+        <v>415.78</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>82.34</v>
+        <v>-33.62</v>
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
     </row>
@@ -4117,20 +4117,20 @@
         <v>8</v>
       </c>
       <c r="D170" s="9" t="n">
-        <v>611.73</v>
+        <v>330.87</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>76.46599999999999</v>
+        <v>41.359</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>494.58</v>
+        <v>342.89</v>
       </c>
       <c r="G170" s="9" t="n">
-        <v>117.15</v>
+        <v>-12.02</v>
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
-          <t>+23.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -4149,20 +4149,20 @@
         <v>8</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>618.16</v>
+        <v>334.08</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>77.27</v>
+        <v>41.76</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>545.5599999999999</v>
+        <v>381.19</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>72.59999999999999</v>
+        <v>-47.11</v>
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
     </row>
@@ -4181,20 +4181,20 @@
         <v>8</v>
       </c>
       <c r="D172" s="9" t="n">
-        <v>690.3200000000001</v>
+        <v>370.16</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>86.29000000000001</v>
+        <v>46.27</v>
       </c>
       <c r="F172" s="9" t="n">
-        <v>423.35</v>
+        <v>286.26</v>
       </c>
       <c r="G172" s="9" t="n">
-        <v>266.97</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
-          <t>+63.1%</t>
+          <t>+29.3%</t>
         </is>
       </c>
     </row>
@@ -4213,20 +4213,20 @@
         <v>8</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>690.45</v>
+        <v>370.23</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>86.306</v>
+        <v>46.279</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>423.45</v>
+        <v>286.33</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>267</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>+63.1%</t>
+          <t>+29.3%</t>
         </is>
       </c>
     </row>
@@ -4245,20 +4245,20 @@
         <v>8</v>
       </c>
       <c r="D174" s="9" t="n">
-        <v>715.5</v>
+        <v>382.75</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>89.438</v>
+        <v>47.844</v>
       </c>
       <c r="F174" s="9" t="n">
-        <v>434.98</v>
+        <v>295.34</v>
       </c>
       <c r="G174" s="9" t="n">
-        <v>280.52</v>
+        <v>87.41</v>
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
-          <t>+64.5%</t>
+          <t>+29.6%</t>
         </is>
       </c>
     </row>
@@ -4277,20 +4277,20 @@
         <v>8</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>575.34</v>
+        <v>312.67</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>71.91800000000001</v>
+        <v>39.084</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>471.09</v>
+        <v>321.94</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>104.25</v>
+        <v>-9.27</v>
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>+22.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
     </row>
@@ -4309,20 +4309,20 @@
         <v>8</v>
       </c>
       <c r="D176" s="9" t="n">
-        <v>588.34</v>
+        <v>319.17</v>
       </c>
       <c r="E176" s="9" t="n">
-        <v>73.54300000000001</v>
+        <v>39.896</v>
       </c>
       <c r="F176" s="9" t="n">
-        <v>513.35</v>
+        <v>355.66</v>
       </c>
       <c r="G176" s="9" t="n">
-        <v>74.98999999999999</v>
+        <v>-36.49</v>
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>+14.6%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
@@ -4341,27 +4341,27 @@
         <v>8</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>9569.75</v>
+        <v>7169.37</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>1196.219</v>
+        <v>896.171</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>523.29</v>
+        <v>363.4</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>9046.459999999999</v>
+        <v>6805.97</v>
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
-          <t>+1728.8%</t>
+          <t>+1872.8%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 8</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 8</t>
         </is>
       </c>
       <c r="D178" s="10" t="n">
@@ -4406,27 +4406,27 @@
         <v>22</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>132.39</v>
+        <v>66.2</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>6.018</v>
+        <v>3.009</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>130.54</v>
+        <v>118.1</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>1.85</v>
+        <v>-51.9</v>
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-43.9%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 22</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 22</t>
         </is>
       </c>
       <c r="D182" s="10" t="n">
@@ -4476,27 +4476,27 @@
         <v>59</v>
       </c>
       <c r="D185" s="9" t="n">
-        <v>194.89</v>
+        <v>97.45</v>
       </c>
       <c r="E185" s="9" t="n">
-        <v>3.303</v>
+        <v>1.652</v>
       </c>
       <c r="F185" s="9" t="n">
-        <v>157.17</v>
+        <v>140.67</v>
       </c>
       <c r="G185" s="9" t="n">
-        <v>37.72</v>
+        <v>-43.22</v>
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>+24.0%</t>
+          <t>-30.7%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 59</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 59</t>
         </is>
       </c>
       <c r="D186" s="10" t="n">
@@ -4541,20 +4541,20 @@
         <v>25</v>
       </c>
       <c r="D189" s="9" t="n">
-        <v>1065.44</v>
+        <v>588.8</v>
       </c>
       <c r="E189" s="9" t="n">
-        <v>42.618</v>
+        <v>23.552</v>
       </c>
       <c r="F189" s="9" t="n">
-        <v>626.83</v>
+        <v>504.25</v>
       </c>
       <c r="G189" s="9" t="n">
-        <v>438.61</v>
+        <v>84.55</v>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>+70.0%</t>
+          <t>+16.8%</t>
         </is>
       </c>
     </row>
@@ -4573,27 +4573,27 @@
         <v>25</v>
       </c>
       <c r="D190" s="9" t="n">
-        <v>840.46</v>
+        <v>512.23</v>
       </c>
       <c r="E190" s="9" t="n">
-        <v>33.618</v>
+        <v>20.489</v>
       </c>
       <c r="F190" s="9" t="n">
-        <v>452.82</v>
+        <v>358.19</v>
       </c>
       <c r="G190" s="9" t="n">
-        <v>387.64</v>
+        <v>154.04</v>
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>+85.6%</t>
+          <t>+43.0%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 25</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 25</t>
         </is>
       </c>
       <c r="D191" s="10" t="n">
@@ -4638,27 +4638,27 @@
         <v>1</v>
       </c>
       <c r="D194" s="9" t="n">
-        <v>453.63</v>
+        <v>299.32</v>
       </c>
       <c r="E194" s="9" t="n">
-        <v>453.63</v>
+        <v>299.32</v>
       </c>
       <c r="F194" s="9" t="n">
-        <v>241.9</v>
+        <v>182.68</v>
       </c>
       <c r="G194" s="9" t="n">
-        <v>211.73</v>
+        <v>116.64</v>
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
-          <t>+87.5%</t>
+          <t>+63.9%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 1</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 1</t>
         </is>
       </c>
       <c r="D195" s="10" t="n">
@@ -4708,27 +4708,27 @@
         <v>100</v>
       </c>
       <c r="D198" s="9" t="n">
-        <v>1361.8</v>
+        <v>876.4400000000001</v>
       </c>
       <c r="E198" s="9" t="n">
-        <v>13.618</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="F198" s="9" t="n">
-        <v>1230.77</v>
+        <v>889.29</v>
       </c>
       <c r="G198" s="9" t="n">
-        <v>131.03</v>
+        <v>-12.85</v>
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>+10.6%</t>
+          <t>-1.4%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 100</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 100</t>
         </is>
       </c>
       <c r="D199" s="10" t="n">
@@ -4773,27 +4773,27 @@
         <v>50</v>
       </c>
       <c r="D202" s="9" t="n">
-        <v>1050.73</v>
+        <v>550.37</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>21.015</v>
+        <v>11.007</v>
       </c>
       <c r="F202" s="9" t="n">
-        <v>724.2</v>
+        <v>573.99</v>
       </c>
       <c r="G202" s="9" t="n">
-        <v>326.53</v>
+        <v>-23.62</v>
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
-          <t>+45.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 50</t>
         </is>
       </c>
       <c r="D203" s="10" t="n">
@@ -4838,20 +4838,20 @@
         <v>350</v>
       </c>
       <c r="D206" s="9" t="n">
-        <v>3776.74</v>
+        <v>2646.95</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>10.791</v>
+        <v>7.563</v>
       </c>
       <c r="F206" s="9" t="n">
-        <v>4645.82</v>
+        <v>3374.38</v>
       </c>
       <c r="G206" s="9" t="n">
-        <v>-869.08</v>
+        <v>-727.4299999999999</v>
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-21.6%</t>
         </is>
       </c>
     </row>
@@ -4870,27 +4870,27 @@
         <v>350</v>
       </c>
       <c r="D207" s="9" t="n">
-        <v>2815.08</v>
+        <v>1864.58</v>
       </c>
       <c r="E207" s="9" t="n">
-        <v>8.042999999999999</v>
+        <v>5.327</v>
       </c>
       <c r="F207" s="9" t="n">
-        <v>2120.92</v>
+        <v>1493.62</v>
       </c>
       <c r="G207" s="9" t="n">
-        <v>694.16</v>
+        <v>370.96</v>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>+32.7%</t>
+          <t>+24.8%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 350</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 350</t>
         </is>
       </c>
       <c r="D208" s="10" t="n">
@@ -4935,27 +4935,27 @@
         <v>50</v>
       </c>
       <c r="D211" s="9" t="n">
-        <v>255.63</v>
+        <v>127.81</v>
       </c>
       <c r="E211" s="9" t="n">
-        <v>5.113</v>
+        <v>2.556</v>
       </c>
       <c r="F211" s="9" t="n">
-        <v>248.28</v>
+        <v>222.66</v>
       </c>
       <c r="G211" s="9" t="n">
-        <v>7.35</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>-42.6%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 50</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 50</t>
         </is>
       </c>
       <c r="D212" s="10" t="n">
@@ -5005,27 +5005,27 @@
         <v>220</v>
       </c>
       <c r="D215" s="9" t="n">
-        <v>5824.4</v>
+        <v>4398.3</v>
       </c>
       <c r="E215" s="9" t="n">
-        <v>26.475</v>
+        <v>19.992</v>
       </c>
       <c r="F215" s="9" t="n">
-        <v>6164.32</v>
+        <v>4386.16</v>
       </c>
       <c r="G215" s="9" t="n">
-        <v>-339.92</v>
+        <v>12.14</v>
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>+0.3%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 220</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 220</t>
         </is>
       </c>
       <c r="D216" s="10" t="n">
@@ -5075,16 +5075,16 @@
         <v>230</v>
       </c>
       <c r="D219" s="9" t="n">
-        <v>1753.9</v>
+        <v>1192.05</v>
       </c>
       <c r="E219" s="9" t="n">
-        <v>7.626</v>
+        <v>5.183</v>
       </c>
       <c r="F219" s="9" t="n">
-        <v>1387.27</v>
+        <v>943.17</v>
       </c>
       <c r="G219" s="9" t="n">
-        <v>366.63</v>
+        <v>248.88</v>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 230</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 230</t>
         </is>
       </c>
       <c r="D220" s="10" t="n">
@@ -5145,20 +5145,20 @@
         <v>75</v>
       </c>
       <c r="D223" s="9" t="n">
-        <v>1444.15</v>
+        <v>937.84</v>
       </c>
       <c r="E223" s="9" t="n">
-        <v>19.255</v>
+        <v>12.505</v>
       </c>
       <c r="F223" s="9" t="n">
-        <v>1163.37</v>
+        <v>766.88</v>
       </c>
       <c r="G223" s="9" t="n">
-        <v>280.78</v>
+        <v>170.96</v>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
-          <t>+24.1%</t>
+          <t>+22.3%</t>
         </is>
       </c>
     </row>
@@ -5177,27 +5177,27 @@
         <v>150</v>
       </c>
       <c r="D224" s="9" t="n">
-        <v>2353.88</v>
+        <v>1499.62</v>
       </c>
       <c r="E224" s="9" t="n">
-        <v>15.693</v>
+        <v>9.997</v>
       </c>
       <c r="F224" s="9" t="n">
-        <v>1970.75</v>
+        <v>1303.63</v>
       </c>
       <c r="G224" s="9" t="n">
-        <v>383.13</v>
+        <v>195.99</v>
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
-          <t>+19.4%</t>
+          <t>+15.0%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 75/150 kit</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 75/150 kit</t>
         </is>
       </c>
       <c r="D225" s="10" t="n">
@@ -5242,27 +5242,27 @@
         <v>500</v>
       </c>
       <c r="D228" s="9" t="n">
-        <v>1259.41</v>
+        <v>702.2</v>
       </c>
       <c r="E228" s="9" t="n">
-        <v>2.519</v>
+        <v>1.404</v>
       </c>
       <c r="F228" s="9" t="n">
-        <v>985.09</v>
+        <v>633.62</v>
       </c>
       <c r="G228" s="9" t="n">
-        <v>274.32</v>
+        <v>68.58</v>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>+27.8%</t>
+          <t>+10.8%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 500</t>
         </is>
       </c>
       <c r="D229" s="10" t="n">
@@ -5312,27 +5312,27 @@
         <v>22000</v>
       </c>
       <c r="D232" s="9" t="n">
-        <v>3416.08</v>
+        <v>2205.73</v>
       </c>
       <c r="E232" s="9" t="n">
-        <v>0.155</v>
+        <v>0.1</v>
       </c>
       <c r="F232" s="9" t="n">
-        <v>2279.73</v>
+        <v>1723.89</v>
       </c>
       <c r="G232" s="9" t="n">
-        <v>1136.35</v>
+        <v>481.84</v>
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>+49.8%</t>
+          <t>+28.0%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 22000</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 22000</t>
         </is>
       </c>
       <c r="D233" s="10" t="n">
@@ -5377,27 +5377,27 @@
         <v>500</v>
       </c>
       <c r="D236" s="9" t="n">
-        <v>1668.47</v>
+        <v>1066.87</v>
       </c>
       <c r="E236" s="9" t="n">
-        <v>3.337</v>
+        <v>2.134</v>
       </c>
       <c r="F236" s="9" t="n">
-        <v>1221.28</v>
+        <v>875.1799999999999</v>
       </c>
       <c r="G236" s="9" t="n">
-        <v>447.19</v>
+        <v>191.68</v>
       </c>
       <c r="H236" s="9" t="inlineStr">
         <is>
-          <t>+36.6%</t>
+          <t>+21.9%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 500</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 500</t>
         </is>
       </c>
       <c r="D237" s="10" t="n">
@@ -5442,20 +5442,20 @@
         <v>1</v>
       </c>
       <c r="D240" s="9" t="n">
-        <v>438.44</v>
+        <v>275.89</v>
       </c>
       <c r="E240" s="9" t="n">
-        <v>438.44</v>
+        <v>275.89</v>
       </c>
       <c r="F240" s="9" t="n">
-        <v>185.27</v>
+        <v>147.22</v>
       </c>
       <c r="G240" s="9" t="n">
-        <v>253.17</v>
+        <v>128.67</v>
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>+136.6%</t>
+          <t>+87.4%</t>
         </is>
       </c>
     </row>
@@ -5474,20 +5474,20 @@
         <v>1</v>
       </c>
       <c r="D241" s="9" t="n">
-        <v>438.44</v>
+        <v>275.89</v>
       </c>
       <c r="E241" s="9" t="n">
-        <v>438.44</v>
+        <v>275.89</v>
       </c>
       <c r="F241" s="9" t="n">
-        <v>185.27</v>
+        <v>147.22</v>
       </c>
       <c r="G241" s="9" t="n">
-        <v>253.17</v>
+        <v>128.67</v>
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
-          <t>+136.6%</t>
+          <t>+87.4%</t>
         </is>
       </c>
     </row>
@@ -5506,27 +5506,27 @@
         <v>1</v>
       </c>
       <c r="D242" s="9" t="n">
-        <v>454.26</v>
+        <v>283.79</v>
       </c>
       <c r="E242" s="9" t="n">
-        <v>454.26</v>
+        <v>283.79</v>
       </c>
       <c r="F242" s="9" t="n">
-        <v>276.12</v>
+        <v>209.96</v>
       </c>
       <c r="G242" s="9" t="n">
-        <v>178.14</v>
+        <v>73.83</v>
       </c>
       <c r="H242" s="9" t="inlineStr">
         <is>
-          <t>+64.5%</t>
+          <t>+35.2%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 1</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 1</t>
         </is>
       </c>
       <c r="D243" s="10" t="n">
@@ -5571,27 +5571,27 @@
         <v>250</v>
       </c>
       <c r="D246" s="9" t="n">
-        <v>3071.43</v>
+        <v>2134.98</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>12.286</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F246" s="9" t="n">
-        <v>2749.42</v>
+        <v>1689.98</v>
       </c>
       <c r="G246" s="9" t="n">
-        <v>322.01</v>
+        <v>445</v>
       </c>
       <c r="H246" s="9" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TOTAL @ qty 250</t>
+          <t xml:space="preserve">    TOTAL SELL @ qty 250</t>
         </is>
       </c>
       <c r="D247" s="10" t="n">

--- a/frontend/public/SPOT_Executive_Summary.xlsx
+++ b/frontend/public/SPOT_Executive_Summary.xlsx
@@ -1095,19 +1095,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J247"/>
+  <dimension ref="A1:I247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1120,7 +1119,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Grouped by SPOT project. COMPONENT ROWS compare COST (SPOT total cost vs iQuote TotalActualCost). TOTAL rows compare SELL PRICE. iQuote components auto-matched by product name + qty (blank = no confident 1:1 match). Δ% = SPOT vs iQuote (+ = SPOT higher).</t>
+          <t>Grouped by SPOT project. COMPONENT ROWS compare COST (SPOT total cost vs iQuote TotalActualCost minus NotInSpotCost). TOTAL rows compare SELL PRICE. iQuote components auto-matched by product name + qty (blank = no confident 1:1 match). Delta % = SPOT vs iQuote (+ = SPOT higher).</t>
         </is>
       </c>
     </row>
@@ -1147,30 +1146,25 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>SPOT $/ea</t>
+          <t>iQuote $</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>iQuote $</t>
+          <t>Delta $</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Δ $</t>
+          <t>Delta %</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Δ %</t>
+          <t>Verdict</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Actual (produced jobs)</t>
         </is>
@@ -1201,17 +1195,14 @@
         <v>2065.18</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>4.01</v>
+        <v>3774.18</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>3797.68</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>-1732.5</v>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>-45.6%</t>
+        <v>-1709</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>-45.3%</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1224,14 @@
         <v>1526.31</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2.964</v>
+        <v>1445.2</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>1468.7</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>57.61</v>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>+3.9%</t>
+        <v>81.11</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
         </is>
       </c>
     </row>
@@ -1265,17 +1253,14 @@
         <v>363.77</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.706</v>
+        <v>220.76</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>244.26</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>119.51</v>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>+48.9%</t>
+        <v>143.01</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>+64.8%</t>
         </is>
       </c>
     </row>
@@ -1288,18 +1273,18 @@
       <c r="D9" s="10" t="n">
         <v>5763.82</v>
       </c>
+      <c r="E9" s="10" t="n">
+        <v>8118.47</v>
+      </c>
       <c r="F9" s="10" t="n">
-        <v>8118.47</v>
-      </c>
-      <c r="G9" s="10" t="n">
         <v>-2354.65</v>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>-29.0%</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1330,17 +1315,14 @@
         <v>1122.58</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>5.346</v>
+        <v>1514.12</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1537.62</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>-415.04</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>-27.0%</t>
+        <v>-391.54</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>-25.9%</t>
         </is>
       </c>
     </row>
@@ -1353,23 +1335,23 @@
       <c r="D13" s="10" t="n">
         <v>1752.51</v>
       </c>
+      <c r="E13" s="10" t="n">
+        <v>1826.19</v>
+      </c>
       <c r="F13" s="10" t="n">
-        <v>1826.19</v>
-      </c>
-      <c r="G13" s="10" t="n">
         <v>-73.68000000000001</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>-4.0%</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>Job 236341: invoiced $1,733, actual cost $2,277 → margin -31%</t>
         </is>
@@ -1400,17 +1382,14 @@
         <v>1745.07</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3.324</v>
+        <v>1647.12</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1670.62</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>74.45</v>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
+        <v>97.95</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>+5.9%</t>
         </is>
       </c>
     </row>
@@ -1423,18 +1402,18 @@
       <c r="D17" s="10" t="n">
         <v>2634.69</v>
       </c>
+      <c r="E17" s="10" t="n">
+        <v>2452.48</v>
+      </c>
       <c r="F17" s="10" t="n">
-        <v>2452.48</v>
-      </c>
-      <c r="G17" s="10" t="n">
         <v>182.21</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>+7.4%</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1465,17 +1444,14 @@
         <v>1913.13</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1.125</v>
+        <v>3183.26</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>3245.03</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>-1331.9</v>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>-41.0%</t>
+        <v>-1270.13</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
@@ -1488,18 +1464,18 @@
       <c r="D21" s="10" t="n">
         <v>2768.73</v>
       </c>
+      <c r="E21" s="10" t="n">
+        <v>4029.71</v>
+      </c>
       <c r="F21" s="10" t="n">
-        <v>4029.71</v>
-      </c>
-      <c r="G21" s="10" t="n">
         <v>-1260.98</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>-31.3%</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1530,17 +1506,14 @@
         <v>2851.94</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>11.408</v>
+        <v>2047.46</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2070.96</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>780.98</v>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>+37.7%</t>
+        <v>804.48</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>+39.3%</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1535,14 @@
         <v>3890.92</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>7.782</v>
+        <v>4010.54</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>4068.04</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>-177.12</v>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>-4.4%</t>
+        <v>-119.62</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>-3.0%</t>
         </is>
       </c>
     </row>
@@ -1585,18 +1555,18 @@
       <c r="D26" s="10" t="n">
         <v>9144.15</v>
       </c>
+      <c r="E26" s="10" t="n">
+        <v>9322.530000000001</v>
+      </c>
       <c r="F26" s="10" t="n">
-        <v>9322.530000000001</v>
-      </c>
-      <c r="G26" s="10" t="n">
         <v>-178.38</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>-1.9%</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1634,17 +1604,14 @@
         <v>949.34</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>12.658</v>
+        <v>743.38</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>766.88</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>182.46</v>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>+23.8%</t>
+        <v>205.96</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>+27.7%</t>
         </is>
       </c>
     </row>
@@ -1666,17 +1633,14 @@
         <v>1358.05</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>9.054</v>
+        <v>1280.13</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1303.63</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>54.42</v>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>+4.2%</t>
+        <v>77.92</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>+6.1%</t>
         </is>
       </c>
     </row>
@@ -1689,18 +1653,18 @@
       <c r="D32" s="10" t="n">
         <v>3515.4</v>
       </c>
+      <c r="E32" s="10" t="n">
+        <v>3134.12</v>
+      </c>
       <c r="F32" s="10" t="n">
-        <v>3134.12</v>
-      </c>
-      <c r="G32" s="10" t="n">
         <v>381.28</v>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>+12.2%</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="H32" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -1731,17 +1695,14 @@
         <v>1376.32</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>4.588</v>
+        <v>1072.54</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1096.04</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>280.28</v>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>+25.6%</t>
+        <v>303.78</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>+28.3%</t>
         </is>
       </c>
     </row>
@@ -1754,18 +1715,18 @@
       <c r="D36" s="10" t="n">
         <v>1952.9</v>
       </c>
+      <c r="E36" s="10" t="n">
+        <v>1548.37</v>
+      </c>
       <c r="F36" s="10" t="n">
-        <v>1548.37</v>
-      </c>
-      <c r="G36" s="10" t="n">
         <v>404.53</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>+26.1%</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1803,17 +1764,14 @@
         <v>1225.43</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>4.085</v>
+        <v>1361</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>1384.5</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>-159.07</v>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>-11.5%</t>
+        <v>-135.57</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>-10.0%</t>
         </is>
       </c>
     </row>
@@ -1826,18 +1784,18 @@
       <c r="D41" s="10" t="n">
         <v>1915.76</v>
       </c>
+      <c r="E41" s="10" t="n">
+        <v>2031.1</v>
+      </c>
       <c r="F41" s="10" t="n">
-        <v>2031.1</v>
-      </c>
-      <c r="G41" s="10" t="n">
         <v>-115.34</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>-5.7%</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1875,17 +1833,14 @@
         <v>614.54</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2.458</v>
+        <v>558.51</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>582.01</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>32.53</v>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>+5.6%</t>
+        <v>56.03</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>+10.0%</t>
         </is>
       </c>
     </row>
@@ -1898,18 +1853,18 @@
       <c r="D46" s="10" t="n">
         <v>991.12</v>
       </c>
+      <c r="E46" s="10" t="n">
+        <v>818.97</v>
+      </c>
       <c r="F46" s="10" t="n">
-        <v>818.97</v>
-      </c>
-      <c r="G46" s="10" t="n">
         <v>172.15</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>+21.0%</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1940,17 +1895,14 @@
         <v>723.21</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>2.066</v>
+        <v>654.9299999999999</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>678.4299999999999</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>44.78</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>+6.6%</t>
+        <v>68.28</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>+10.4%</t>
         </is>
       </c>
     </row>
@@ -1963,18 +1915,18 @@
       <c r="D50" s="10" t="n">
         <v>1208.46</v>
       </c>
+      <c r="E50" s="10" t="n">
+        <v>958.6</v>
+      </c>
       <c r="F50" s="10" t="n">
-        <v>958.6</v>
-      </c>
-      <c r="G50" s="10" t="n">
         <v>249.86</v>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>+26.1%</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2005,17 +1957,14 @@
         <v>858.3</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>1.717</v>
+        <v>799.55</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>823.05</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>35.25</v>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>+4.3%</t>
+        <v>58.75</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>+7.3%</t>
         </is>
       </c>
     </row>
@@ -2028,18 +1977,18 @@
       <c r="D54" s="10" t="n">
         <v>1478.65</v>
       </c>
+      <c r="E54" s="10" t="n">
+        <v>1168.02</v>
+      </c>
       <c r="F54" s="10" t="n">
-        <v>1168.02</v>
-      </c>
-      <c r="G54" s="10" t="n">
         <v>310.63</v>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>+26.6%</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2070,17 +2019,14 @@
         <v>1074.46</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>1.433</v>
+        <v>1040.59</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1064.09</v>
-      </c>
-      <c r="G57" s="9" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>+1.0%</t>
+        <v>33.87</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
         </is>
       </c>
     </row>
@@ -2093,18 +2039,18 @@
       <c r="D58" s="10" t="n">
         <v>1565.74</v>
       </c>
+      <c r="E58" s="10" t="n">
+        <v>1517.07</v>
+      </c>
       <c r="F58" s="10" t="n">
-        <v>1517.07</v>
-      </c>
-      <c r="G58" s="10" t="n">
         <v>48.67</v>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>+3.2%</t>
         </is>
       </c>
-      <c r="I58" s="12" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2134,9 +2080,6 @@
       <c r="D61" s="9" t="n">
         <v>9499.35</v>
       </c>
-      <c r="E61" s="9" t="n">
-        <v>6.031</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
@@ -2155,9 +2098,6 @@
       <c r="D62" s="9" t="n">
         <v>4925.14</v>
       </c>
-      <c r="E62" s="9" t="n">
-        <v>9.381</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
@@ -2177,17 +2117,14 @@
         <v>2748.58</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>5.235</v>
+        <v>3683.4</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3742.37</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>-993.79</v>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>-26.6%</t>
+        <v>-934.8200000000001</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>-25.4%</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2146,14 @@
         <v>2748.58</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>5.235</v>
+        <v>3683.4</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>3742.37</v>
-      </c>
-      <c r="G64" s="9" t="n">
-        <v>-993.79</v>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>-26.6%</t>
+        <v>-934.8200000000001</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>-25.4%</t>
         </is>
       </c>
     </row>
@@ -2241,17 +2175,14 @@
         <v>2619.45</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>4.989</v>
+        <v>3432.33</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>3479.43</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>-859.98</v>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>-24.7%</t>
+        <v>-812.88</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>-23.7%</t>
         </is>
       </c>
     </row>
@@ -2272,9 +2203,6 @@
       <c r="D66" s="9" t="n">
         <v>2831.61</v>
       </c>
-      <c r="E66" s="9" t="n">
-        <v>5.394</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -2285,18 +2213,18 @@
       <c r="D67" s="10" t="n">
         <v>34381.73</v>
       </c>
+      <c r="E67" s="10" t="n">
+        <v>40873.15</v>
+      </c>
       <c r="F67" s="10" t="n">
-        <v>40873.15</v>
-      </c>
-      <c r="G67" s="10" t="n">
         <v>-6491.42</v>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>-15.9%</t>
         </is>
       </c>
-      <c r="I67" s="15" t="inlineStr">
+      <c r="H67" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -2333,9 +2261,6 @@
       <c r="D71" s="9" t="n">
         <v>317.63</v>
       </c>
-      <c r="E71" s="9" t="n">
-        <v>158.815</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
@@ -2355,17 +2280,14 @@
         <v>328.1</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>41.013</v>
+        <v>186.33</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>209.83</v>
-      </c>
-      <c r="G72" s="9" t="n">
-        <v>118.27</v>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>+56.4%</t>
+        <v>141.77</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>+76.1%</t>
         </is>
       </c>
     </row>
@@ -2387,17 +2309,14 @@
         <v>360.4</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>90.09999999999999</v>
+        <v>230.06</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>253.56</v>
-      </c>
-      <c r="G73" s="9" t="n">
-        <v>106.84</v>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>+42.1%</t>
+        <v>130.34</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>+56.7%</t>
         </is>
       </c>
     </row>
@@ -2419,17 +2338,14 @@
         <v>313.81</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>156.905</v>
+        <v>180.48</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>217.98</v>
-      </c>
-      <c r="G74" s="9" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>+44.0%</t>
+        <v>133.33</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>+73.9%</t>
         </is>
       </c>
     </row>
@@ -2451,15 +2367,12 @@
         <v>275.25</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>137.625</v>
+        <v>164.97</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>164.97</v>
-      </c>
-      <c r="G75" s="9" t="n">
         <v>110.28</v>
       </c>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>+66.8%</t>
         </is>
@@ -2483,17 +2396,14 @@
         <v>276.67</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>138.335</v>
+        <v>168.89</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>192.39</v>
-      </c>
-      <c r="G76" s="9" t="n">
-        <v>84.28</v>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>+43.8%</t>
+        <v>107.78</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>+63.8%</t>
         </is>
       </c>
     </row>
@@ -2506,18 +2416,18 @@
       <c r="D77" s="10" t="n">
         <v>2859.44</v>
       </c>
+      <c r="E77" s="10" t="n">
+        <v>1803.46</v>
+      </c>
       <c r="F77" s="10" t="n">
-        <v>1803.46</v>
-      </c>
-      <c r="G77" s="10" t="n">
         <v>1055.98</v>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>+58.6%</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr">
+      <c r="H77" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2547,9 +2457,6 @@
       <c r="D80" s="9" t="n">
         <v>2333.29</v>
       </c>
-      <c r="E80" s="9" t="n">
-        <v>2.542</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
@@ -2568,9 +2475,6 @@
       <c r="D81" s="9" t="n">
         <v>4029.25</v>
       </c>
-      <c r="E81" s="9" t="n">
-        <v>2.302</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
@@ -2581,18 +2485,18 @@
       <c r="D82" s="10" t="n">
         <v>9023.129999999999</v>
       </c>
+      <c r="E82" s="10" t="n">
+        <v>16354.54</v>
+      </c>
       <c r="F82" s="10" t="n">
-        <v>16354.54</v>
-      </c>
-      <c r="G82" s="10" t="n">
         <v>-7331.41</v>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>-44.8%</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
+      <c r="H82" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2630,17 +2534,14 @@
         <v>2340.35</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>3.901</v>
+        <v>1965.25</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>1988.75</v>
-      </c>
-      <c r="G86" s="9" t="n">
-        <v>351.6</v>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>+17.7%</t>
+        <v>375.1</v>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>+19.1%</t>
         </is>
       </c>
     </row>
@@ -2653,18 +2554,18 @@
       <c r="D87" s="10" t="n">
         <v>3418.16</v>
       </c>
+      <c r="E87" s="10" t="n">
+        <v>2931.56</v>
+      </c>
       <c r="F87" s="10" t="n">
-        <v>2931.56</v>
-      </c>
-      <c r="G87" s="10" t="n">
         <v>486.6</v>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="G87" s="10" t="inlineStr">
         <is>
           <t>+16.6%</t>
         </is>
       </c>
-      <c r="I87" s="15" t="inlineStr">
+      <c r="H87" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -2695,17 +2596,14 @@
         <v>1453.25</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>4.844</v>
+        <v>1236.41</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>1259.91</v>
-      </c>
-      <c r="G90" s="9" t="n">
-        <v>193.34</v>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>+15.3%</t>
+        <v>216.84</v>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>+17.5%</t>
         </is>
       </c>
     </row>
@@ -2727,15 +2625,12 @@
         <v>389.75</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>12.992</v>
+        <v>395.56</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>395.56</v>
-      </c>
-      <c r="G91" s="9" t="n">
         <v>-5.81</v>
       </c>
-      <c r="H91" s="9" t="inlineStr">
+      <c r="G91" s="9" t="inlineStr">
         <is>
           <t>-1.5%</t>
         </is>
@@ -2750,18 +2645,18 @@
       <c r="D92" s="10" t="n">
         <v>3006.89</v>
       </c>
+      <c r="E92" s="10" t="n">
+        <v>2570.16</v>
+      </c>
       <c r="F92" s="10" t="n">
-        <v>2570.16</v>
-      </c>
-      <c r="G92" s="10" t="n">
         <v>436.73</v>
       </c>
-      <c r="H92" s="10" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>+17.0%</t>
         </is>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="H92" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -2792,17 +2687,14 @@
         <v>2686.21</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>2.066</v>
+        <v>3611.31</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>3634.81</v>
-      </c>
-      <c r="G95" s="9" t="n">
-        <v>-948.6</v>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>-26.1%</t>
+        <v>-925.1</v>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>-25.6%</t>
         </is>
       </c>
     </row>
@@ -2815,18 +2707,18 @@
       <c r="D96" s="10" t="n">
         <v>3661.24</v>
       </c>
+      <c r="E96" s="10" t="n">
+        <v>5528.87</v>
+      </c>
       <c r="F96" s="10" t="n">
-        <v>5528.87</v>
-      </c>
-      <c r="G96" s="10" t="n">
         <v>-1867.63</v>
       </c>
-      <c r="H96" s="10" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>-33.8%</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr">
+      <c r="H96" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2856,9 +2748,6 @@
       <c r="D99" s="9" t="n">
         <v>2833.71</v>
       </c>
-      <c r="E99" s="9" t="n">
-        <v>11.335</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
@@ -2877,9 +2766,6 @@
       <c r="D100" s="9" t="n">
         <v>2833.71</v>
       </c>
-      <c r="E100" s="9" t="n">
-        <v>11.335</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -2890,18 +2776,18 @@
       <c r="D101" s="10" t="n">
         <v>7744.83</v>
       </c>
+      <c r="E101" s="10" t="n">
+        <v>9166.92</v>
+      </c>
       <c r="F101" s="10" t="n">
-        <v>9166.92</v>
-      </c>
-      <c r="G101" s="10" t="n">
         <v>-1422.09</v>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="G101" s="10" t="inlineStr">
         <is>
           <t>-15.5%</t>
         </is>
       </c>
-      <c r="I101" s="15" t="inlineStr">
+      <c r="H101" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -2931,9 +2817,6 @@
       <c r="D104" s="9" t="n">
         <v>5253.93</v>
       </c>
-      <c r="E104" s="9" t="n">
-        <v>10.508</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
@@ -2952,9 +2835,6 @@
       <c r="D105" s="9" t="n">
         <v>5253.93</v>
       </c>
-      <c r="E105" s="9" t="n">
-        <v>10.508</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
@@ -2965,18 +2845,18 @@
       <c r="D106" s="10" t="n">
         <v>14000.47</v>
       </c>
+      <c r="E106" s="10" t="n">
+        <v>14908.08</v>
+      </c>
       <c r="F106" s="10" t="n">
-        <v>14908.08</v>
-      </c>
-      <c r="G106" s="10" t="n">
         <v>-907.61</v>
       </c>
-      <c r="H106" s="10" t="inlineStr">
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>-6.1%</t>
         </is>
       </c>
-      <c r="I106" s="12" t="inlineStr">
+      <c r="H106" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3006,9 +2886,6 @@
       <c r="D109" s="9" t="n">
         <v>1283.18</v>
       </c>
-      <c r="E109" s="9" t="n">
-        <v>12.832</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -3027,9 +2904,6 @@
       <c r="D110" s="9" t="n">
         <v>751.9299999999999</v>
       </c>
-      <c r="E110" s="9" t="n">
-        <v>7.519</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -3040,18 +2914,18 @@
       <c r="D111" s="10" t="n">
         <v>3337.89</v>
       </c>
+      <c r="E111" s="10" t="n">
+        <v>3463.91</v>
+      </c>
       <c r="F111" s="10" t="n">
-        <v>3463.91</v>
-      </c>
-      <c r="G111" s="10" t="n">
         <v>-126.02</v>
       </c>
-      <c r="H111" s="10" t="inlineStr">
+      <c r="G111" s="10" t="inlineStr">
         <is>
           <t>-3.6%</t>
         </is>
       </c>
-      <c r="I111" s="12" t="inlineStr">
+      <c r="H111" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3081,9 +2955,6 @@
       <c r="D114" s="9" t="n">
         <v>2233.83</v>
       </c>
-      <c r="E114" s="9" t="n">
-        <v>11.169</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
@@ -3102,9 +2973,6 @@
       <c r="D115" s="9" t="n">
         <v>1141.07</v>
       </c>
-      <c r="E115" s="9" t="n">
-        <v>5.705</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -3115,18 +2983,18 @@
       <c r="D116" s="10" t="n">
         <v>4996.39</v>
       </c>
+      <c r="E116" s="10" t="n">
+        <v>5894.43</v>
+      </c>
       <c r="F116" s="10" t="n">
-        <v>5894.43</v>
-      </c>
-      <c r="G116" s="10" t="n">
         <v>-898.04</v>
       </c>
-      <c r="H116" s="10" t="inlineStr">
+      <c r="G116" s="10" t="inlineStr">
         <is>
           <t>-15.2%</t>
         </is>
       </c>
-      <c r="I116" s="15" t="inlineStr">
+      <c r="H116" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -3156,9 +3024,6 @@
       <c r="D119" s="9" t="n">
         <v>805.13</v>
       </c>
-      <c r="E119" s="9" t="n">
-        <v>16.103</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
@@ -3177,9 +3042,6 @@
       <c r="D120" s="9" t="n">
         <v>557.36</v>
       </c>
-      <c r="E120" s="9" t="n">
-        <v>11.147</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -3190,18 +3052,18 @@
       <c r="D121" s="10" t="n">
         <v>2449.07</v>
       </c>
+      <c r="E121" s="10" t="n">
+        <v>2142.17</v>
+      </c>
       <c r="F121" s="10" t="n">
-        <v>2142.17</v>
-      </c>
-      <c r="G121" s="10" t="n">
         <v>306.9</v>
       </c>
-      <c r="H121" s="10" t="inlineStr">
+      <c r="G121" s="10" t="inlineStr">
         <is>
           <t>+14.3%</t>
         </is>
       </c>
-      <c r="I121" s="15" t="inlineStr">
+      <c r="H121" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -3232,17 +3094,14 @@
         <v>4262.3</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>6.089</v>
+        <v>3618.54</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>3689.77</v>
-      </c>
-      <c r="G124" s="9" t="n">
-        <v>572.53</v>
-      </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>+15.5%</t>
+        <v>643.76</v>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>+17.8%</t>
         </is>
       </c>
     </row>
@@ -3255,18 +3114,18 @@
       <c r="D125" s="10" t="n">
         <v>5753.95</v>
       </c>
+      <c r="E125" s="10" t="n">
+        <v>4904.67</v>
+      </c>
       <c r="F125" s="10" t="n">
-        <v>4904.67</v>
-      </c>
-      <c r="G125" s="10" t="n">
         <v>849.28</v>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="G125" s="10" t="inlineStr">
         <is>
           <t>+17.3%</t>
         </is>
       </c>
-      <c r="I125" s="15" t="inlineStr">
+      <c r="H125" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -3297,17 +3156,14 @@
         <v>651.79</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>1.304</v>
+        <v>771.99</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>795.49</v>
-      </c>
-      <c r="G128" s="9" t="n">
-        <v>-143.7</v>
-      </c>
-      <c r="H128" s="9" t="inlineStr">
-        <is>
-          <t>-18.1%</t>
+        <v>-120.2</v>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -3320,18 +3176,18 @@
       <c r="D129" s="10" t="n">
         <v>1183.59</v>
       </c>
+      <c r="E129" s="10" t="n">
+        <v>1003.06</v>
+      </c>
       <c r="F129" s="10" t="n">
-        <v>1003.06</v>
-      </c>
-      <c r="G129" s="10" t="n">
         <v>180.53</v>
       </c>
-      <c r="H129" s="10" t="inlineStr">
+      <c r="G129" s="10" t="inlineStr">
         <is>
           <t>+18.0%</t>
         </is>
       </c>
-      <c r="I129" s="15" t="inlineStr">
+      <c r="H129" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -3362,17 +3218,14 @@
         <v>2206.38</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>8.826000000000001</v>
+        <v>1666.48</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>1689.98</v>
-      </c>
-      <c r="G132" s="9" t="n">
-        <v>516.4</v>
-      </c>
-      <c r="H132" s="9" t="inlineStr">
-        <is>
-          <t>+30.6%</t>
+        <v>539.9</v>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>+32.4%</t>
         </is>
       </c>
     </row>
@@ -3385,18 +3238,18 @@
       <c r="D133" s="10" t="n">
         <v>3176.43</v>
       </c>
+      <c r="E133" s="10" t="n">
+        <v>2749.42</v>
+      </c>
       <c r="F133" s="10" t="n">
-        <v>2749.42</v>
-      </c>
-      <c r="G133" s="10" t="n">
         <v>427.01</v>
       </c>
-      <c r="H133" s="10" t="inlineStr">
+      <c r="G133" s="10" t="inlineStr">
         <is>
           <t>+15.5%</t>
         </is>
       </c>
-      <c r="I133" s="15" t="inlineStr">
+      <c r="H133" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -3427,17 +3280,14 @@
         <v>5110.18</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>20.441</v>
+        <v>4490.83</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>4548.46</v>
-      </c>
-      <c r="G136" s="9" t="n">
-        <v>561.72</v>
-      </c>
-      <c r="H136" s="9" t="inlineStr">
-        <is>
-          <t>+12.3%</t>
+        <v>619.35</v>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>+13.8%</t>
         </is>
       </c>
     </row>
@@ -3450,23 +3300,23 @@
       <c r="D137" s="10" t="n">
         <v>6773.57</v>
       </c>
+      <c r="E137" s="10" t="n">
+        <v>6549.08</v>
+      </c>
       <c r="F137" s="10" t="n">
-        <v>6549.08</v>
-      </c>
-      <c r="G137" s="10" t="n">
         <v>224.49</v>
       </c>
-      <c r="H137" s="10" t="inlineStr">
+      <c r="G137" s="10" t="inlineStr">
         <is>
           <t>+3.4%</t>
         </is>
       </c>
-      <c r="I137" s="12" t="inlineStr">
+      <c r="H137" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J137" s="13" t="inlineStr">
+      <c r="I137" s="13" t="inlineStr">
         <is>
           <t>Job 236943: invoiced $4,353, actual cost $9,468 → margin -118%</t>
         </is>
@@ -3497,17 +3347,14 @@
         <v>6063.51</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>20.212</v>
+        <v>5172.88</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>5237.31</v>
-      </c>
-      <c r="G140" s="9" t="n">
-        <v>826.2</v>
-      </c>
-      <c r="H140" s="9" t="inlineStr">
-        <is>
-          <t>+15.8%</t>
+        <v>890.63</v>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>+17.2%</t>
         </is>
       </c>
     </row>
@@ -3520,18 +3367,18 @@
       <c r="D141" s="10" t="n">
         <v>8044.68</v>
       </c>
+      <c r="E141" s="10" t="n">
+        <v>7577.35</v>
+      </c>
       <c r="F141" s="10" t="n">
-        <v>7577.35</v>
-      </c>
-      <c r="G141" s="10" t="n">
         <v>467.33</v>
       </c>
-      <c r="H141" s="10" t="inlineStr">
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>+6.2%</t>
         </is>
       </c>
-      <c r="I141" s="12" t="inlineStr">
+      <c r="H141" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3561,9 +3408,6 @@
       <c r="D144" s="9" t="n">
         <v>3529.3</v>
       </c>
-      <c r="E144" s="9" t="n">
-        <v>3.529</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
@@ -3582,9 +3426,6 @@
       <c r="D145" s="9" t="n">
         <v>2612.82</v>
       </c>
-      <c r="E145" s="9" t="n">
-        <v>3.733</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -3595,18 +3436,18 @@
       <c r="D146" s="10" t="n">
         <v>8481.110000000001</v>
       </c>
+      <c r="E146" s="10" t="n">
+        <v>9299.35</v>
+      </c>
       <c r="F146" s="10" t="n">
-        <v>9299.35</v>
-      </c>
-      <c r="G146" s="10" t="n">
         <v>-818.24</v>
       </c>
-      <c r="H146" s="10" t="inlineStr">
+      <c r="G146" s="10" t="inlineStr">
         <is>
           <t>-8.8%</t>
         </is>
       </c>
-      <c r="I146" s="12" t="inlineStr">
+      <c r="H146" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3637,17 +3478,14 @@
         <v>620.37</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>12.407</v>
+        <v>550.49</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>573.99</v>
-      </c>
-      <c r="G149" s="9" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="H149" s="9" t="inlineStr">
-        <is>
-          <t>+8.1%</t>
+        <v>69.88</v>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>+12.7%</t>
         </is>
       </c>
     </row>
@@ -3660,18 +3498,18 @@
       <c r="D150" s="10" t="n">
         <v>1120.73</v>
       </c>
+      <c r="E150" s="10" t="n">
+        <v>724.2</v>
+      </c>
       <c r="F150" s="10" t="n">
-        <v>724.2</v>
-      </c>
-      <c r="G150" s="10" t="n">
         <v>396.53</v>
       </c>
-      <c r="H150" s="10" t="inlineStr">
+      <c r="G150" s="10" t="inlineStr">
         <is>
           <t>+54.8%</t>
         </is>
       </c>
-      <c r="I150" s="11" t="inlineStr">
+      <c r="H150" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3702,17 +3540,14 @@
         <v>716.83</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>1.434</v>
+        <v>610.12</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>633.62</v>
-      </c>
-      <c r="G153" s="9" t="n">
-        <v>83.20999999999999</v>
-      </c>
-      <c r="H153" s="9" t="inlineStr">
-        <is>
-          <t>+13.1%</t>
+        <v>106.71</v>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>+17.5%</t>
         </is>
       </c>
     </row>
@@ -3725,18 +3560,18 @@
       <c r="D154" s="10" t="n">
         <v>1288.67</v>
       </c>
+      <c r="E154" s="10" t="n">
+        <v>985.09</v>
+      </c>
       <c r="F154" s="10" t="n">
-        <v>985.09</v>
-      </c>
-      <c r="G154" s="10" t="n">
         <v>303.58</v>
       </c>
-      <c r="H154" s="10" t="inlineStr">
+      <c r="G154" s="10" t="inlineStr">
         <is>
           <t>+30.8%</t>
         </is>
       </c>
-      <c r="I154" s="11" t="inlineStr">
+      <c r="H154" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3767,17 +3602,14 @@
         <v>497.02</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>33.135</v>
+        <v>498.08</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>521.58</v>
-      </c>
-      <c r="G157" s="9" t="n">
-        <v>-24.56</v>
-      </c>
-      <c r="H157" s="9" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
+        <v>-1.06</v>
+      </c>
+      <c r="G157" s="9" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -3799,17 +3631,14 @@
         <v>443.01</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>29.534</v>
+        <v>417.22</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>440.72</v>
-      </c>
-      <c r="G158" s="9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H158" s="9" t="inlineStr">
-        <is>
-          <t>+0.5%</t>
+        <v>25.79</v>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
         </is>
       </c>
     </row>
@@ -3831,17 +3660,14 @@
         <v>447.48</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>29.832</v>
+        <v>425.06</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>482.56</v>
-      </c>
-      <c r="G159" s="9" t="n">
-        <v>-35.08</v>
-      </c>
-      <c r="H159" s="9" t="inlineStr">
-        <is>
-          <t>-7.3%</t>
+        <v>22.42</v>
+      </c>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>+5.3%</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3689,14 @@
         <v>494.09</v>
       </c>
       <c r="E160" s="9" t="n">
-        <v>32.939</v>
+        <v>358.79</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>382.29</v>
-      </c>
-      <c r="G160" s="9" t="n">
-        <v>111.8</v>
-      </c>
-      <c r="H160" s="9" t="inlineStr">
-        <is>
-          <t>+29.2%</t>
+        <v>135.3</v>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>+37.7%</t>
         </is>
       </c>
     </row>
@@ -3895,17 +3718,14 @@
         <v>494.21</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>32.947</v>
+        <v>358.93</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>382.43</v>
-      </c>
-      <c r="G161" s="9" t="n">
-        <v>111.78</v>
-      </c>
-      <c r="H161" s="9" t="inlineStr">
-        <is>
-          <t>+29.2%</t>
+        <v>135.28</v>
+      </c>
+      <c r="G161" s="9" t="inlineStr">
+        <is>
+          <t>+37.7%</t>
         </is>
       </c>
     </row>
@@ -3927,17 +3747,14 @@
         <v>511.21</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>34.081</v>
+        <v>375.11</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>398.61</v>
-      </c>
-      <c r="G162" s="9" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="H162" s="9" t="inlineStr">
-        <is>
-          <t>+28.2%</t>
+        <v>136.1</v>
+      </c>
+      <c r="G162" s="9" t="inlineStr">
+        <is>
+          <t>+36.3%</t>
         </is>
       </c>
     </row>
@@ -3959,17 +3776,14 @@
         <v>412.25</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>27.483</v>
+        <v>314.66</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>372.16</v>
-      </c>
-      <c r="G163" s="9" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="H163" s="9" t="inlineStr">
-        <is>
-          <t>+10.8%</t>
+        <v>97.59</v>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
+        <is>
+          <t>+31.0%</t>
         </is>
       </c>
     </row>
@@ -3991,17 +3805,14 @@
         <v>424.08</v>
       </c>
       <c r="E164" s="9" t="n">
-        <v>28.272</v>
+        <v>377.83</v>
       </c>
       <c r="F164" s="9" t="n">
-        <v>435.33</v>
-      </c>
-      <c r="G164" s="9" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="H164" s="9" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
+        <v>46.25</v>
+      </c>
+      <c r="G164" s="9" t="inlineStr">
+        <is>
+          <t>+12.2%</t>
         </is>
       </c>
     </row>
@@ -4023,17 +3834,14 @@
         <v>5871.75</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>391.45</v>
+        <v>391.66</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>449.16</v>
-      </c>
-      <c r="G165" s="9" t="n">
-        <v>5422.59</v>
-      </c>
-      <c r="H165" s="9" t="inlineStr">
-        <is>
-          <t>+1207.3%</t>
+        <v>5480.09</v>
+      </c>
+      <c r="G165" s="9" t="inlineStr">
+        <is>
+          <t>+1399.2%</t>
         </is>
       </c>
     </row>
@@ -4046,18 +3854,18 @@
       <c r="D166" s="10" t="n">
         <v>14889.07</v>
       </c>
+      <c r="E166" s="10" t="n">
+        <v>5653.51</v>
+      </c>
       <c r="F166" s="10" t="n">
-        <v>5653.51</v>
-      </c>
-      <c r="G166" s="10" t="n">
         <v>9235.559999999999</v>
       </c>
-      <c r="H166" s="10" t="inlineStr">
+      <c r="G166" s="10" t="inlineStr">
         <is>
           <t>+163.4%</t>
         </is>
       </c>
-      <c r="I166" s="11" t="inlineStr">
+      <c r="H166" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4088,17 +3896,14 @@
         <v>382.16</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>47.77</v>
+        <v>392.28</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>415.78</v>
-      </c>
-      <c r="G169" s="9" t="n">
-        <v>-33.62</v>
-      </c>
-      <c r="H169" s="9" t="inlineStr">
-        <is>
-          <t>-8.1%</t>
+        <v>-10.12</v>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
         </is>
       </c>
     </row>
@@ -4120,17 +3925,14 @@
         <v>330.87</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>41.359</v>
+        <v>319.39</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>342.89</v>
-      </c>
-      <c r="G170" s="9" t="n">
-        <v>-12.02</v>
-      </c>
-      <c r="H170" s="9" t="inlineStr">
-        <is>
-          <t>-3.5%</t>
+        <v>11.48</v>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
         </is>
       </c>
     </row>
@@ -4152,17 +3954,14 @@
         <v>334.08</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>41.76</v>
+        <v>323.69</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>381.19</v>
-      </c>
-      <c r="G171" s="9" t="n">
-        <v>-47.11</v>
-      </c>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t>-12.4%</t>
+        <v>10.39</v>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
         </is>
       </c>
     </row>
@@ -4184,17 +3983,14 @@
         <v>370.16</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>46.27</v>
+        <v>262.76</v>
       </c>
       <c r="F172" s="9" t="n">
-        <v>286.26</v>
-      </c>
-      <c r="G172" s="9" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="H172" s="9" t="inlineStr">
-        <is>
-          <t>+29.3%</t>
+        <v>107.4</v>
+      </c>
+      <c r="G172" s="9" t="inlineStr">
+        <is>
+          <t>+40.9%</t>
         </is>
       </c>
     </row>
@@ -4216,17 +4012,14 @@
         <v>370.23</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>46.279</v>
+        <v>262.83</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>286.33</v>
-      </c>
-      <c r="G173" s="9" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="H173" s="9" t="inlineStr">
-        <is>
-          <t>+29.3%</t>
+        <v>107.4</v>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>+40.9%</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4041,14 @@
         <v>382.75</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>47.844</v>
+        <v>271.84</v>
       </c>
       <c r="F174" s="9" t="n">
-        <v>295.34</v>
-      </c>
-      <c r="G174" s="9" t="n">
-        <v>87.41</v>
-      </c>
-      <c r="H174" s="9" t="inlineStr">
-        <is>
-          <t>+29.6%</t>
+        <v>110.91</v>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>+40.8%</t>
         </is>
       </c>
     </row>
@@ -4280,17 +4070,14 @@
         <v>312.67</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>39.084</v>
+        <v>264.44</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>321.94</v>
-      </c>
-      <c r="G175" s="9" t="n">
-        <v>-9.27</v>
-      </c>
-      <c r="H175" s="9" t="inlineStr">
-        <is>
-          <t>-2.9%</t>
+        <v>48.23</v>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>+18.2%</t>
         </is>
       </c>
     </row>
@@ -4312,17 +4099,14 @@
         <v>319.17</v>
       </c>
       <c r="E176" s="9" t="n">
-        <v>39.896</v>
+        <v>298.16</v>
       </c>
       <c r="F176" s="9" t="n">
-        <v>355.66</v>
-      </c>
-      <c r="G176" s="9" t="n">
-        <v>-36.49</v>
-      </c>
-      <c r="H176" s="9" t="inlineStr">
-        <is>
-          <t>-10.3%</t>
+        <v>21.01</v>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>+7.0%</t>
         </is>
       </c>
     </row>
@@ -4344,17 +4128,14 @@
         <v>7169.37</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>896.171</v>
+        <v>305.9</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>363.4</v>
-      </c>
-      <c r="G177" s="9" t="n">
-        <v>6805.97</v>
-      </c>
-      <c r="H177" s="9" t="inlineStr">
-        <is>
-          <t>+1872.8%</t>
+        <v>6863.47</v>
+      </c>
+      <c r="G177" s="9" t="inlineStr">
+        <is>
+          <t>+2243.7%</t>
         </is>
       </c>
     </row>
@@ -4367,18 +4148,18 @@
       <c r="D178" s="10" t="n">
         <v>14773.92</v>
       </c>
+      <c r="E178" s="10" t="n">
+        <v>4461.64</v>
+      </c>
       <c r="F178" s="10" t="n">
-        <v>4461.64</v>
-      </c>
-      <c r="G178" s="10" t="n">
         <v>10312.28</v>
       </c>
-      <c r="H178" s="10" t="inlineStr">
+      <c r="G178" s="10" t="inlineStr">
         <is>
           <t>+231.1%</t>
         </is>
       </c>
-      <c r="I178" s="11" t="inlineStr">
+      <c r="H178" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4409,17 +4190,14 @@
         <v>66.2</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>3.009</v>
+        <v>115.85</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>118.1</v>
-      </c>
-      <c r="G181" s="9" t="n">
-        <v>-51.9</v>
-      </c>
-      <c r="H181" s="9" t="inlineStr">
-        <is>
-          <t>-43.9%</t>
+        <v>-49.65</v>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>-42.9%</t>
         </is>
       </c>
     </row>
@@ -4432,23 +4210,23 @@
       <c r="D182" s="10" t="n">
         <v>132.39</v>
       </c>
+      <c r="E182" s="10" t="n">
+        <v>130.54</v>
+      </c>
       <c r="F182" s="10" t="n">
-        <v>130.54</v>
-      </c>
-      <c r="G182" s="10" t="n">
         <v>1.85</v>
       </c>
-      <c r="H182" s="10" t="inlineStr">
+      <c r="G182" s="10" t="inlineStr">
         <is>
           <t>+1.4%</t>
         </is>
       </c>
-      <c r="I182" s="12" t="inlineStr">
+      <c r="H182" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J182" s="13" t="inlineStr">
+      <c r="I182" s="13" t="inlineStr">
         <is>
           <t>Job 237252: invoiced $142, actual cost $164 → margin -15%</t>
         </is>
@@ -4479,17 +4257,14 @@
         <v>97.45</v>
       </c>
       <c r="E185" s="9" t="n">
-        <v>1.652</v>
+        <v>138.42</v>
       </c>
       <c r="F185" s="9" t="n">
-        <v>140.67</v>
-      </c>
-      <c r="G185" s="9" t="n">
-        <v>-43.22</v>
-      </c>
-      <c r="H185" s="9" t="inlineStr">
-        <is>
-          <t>-30.7%</t>
+        <v>-40.97</v>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>-29.6%</t>
         </is>
       </c>
     </row>
@@ -4502,18 +4277,18 @@
       <c r="D186" s="10" t="n">
         <v>194.89</v>
       </c>
+      <c r="E186" s="10" t="n">
+        <v>157.17</v>
+      </c>
       <c r="F186" s="10" t="n">
-        <v>157.17</v>
-      </c>
-      <c r="G186" s="10" t="n">
         <v>37.72</v>
       </c>
-      <c r="H186" s="10" t="inlineStr">
+      <c r="G186" s="10" t="inlineStr">
         <is>
           <t>+24.0%</t>
         </is>
       </c>
-      <c r="I186" s="11" t="inlineStr">
+      <c r="H186" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4544,17 +4319,14 @@
         <v>588.8</v>
       </c>
       <c r="E189" s="9" t="n">
-        <v>23.552</v>
+        <v>480.75</v>
       </c>
       <c r="F189" s="9" t="n">
-        <v>504.25</v>
-      </c>
-      <c r="G189" s="9" t="n">
-        <v>84.55</v>
-      </c>
-      <c r="H189" s="9" t="inlineStr">
-        <is>
-          <t>+16.8%</t>
+        <v>108.05</v>
+      </c>
+      <c r="G189" s="9" t="inlineStr">
+        <is>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
@@ -4576,17 +4348,14 @@
         <v>512.23</v>
       </c>
       <c r="E190" s="9" t="n">
-        <v>20.489</v>
+        <v>334.69</v>
       </c>
       <c r="F190" s="9" t="n">
-        <v>358.19</v>
-      </c>
-      <c r="G190" s="9" t="n">
-        <v>154.04</v>
-      </c>
-      <c r="H190" s="9" t="inlineStr">
-        <is>
-          <t>+43.0%</t>
+        <v>177.54</v>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>+53.0%</t>
         </is>
       </c>
     </row>
@@ -4599,18 +4368,18 @@
       <c r="D191" s="10" t="n">
         <v>1905.9</v>
       </c>
+      <c r="E191" s="10" t="n">
+        <v>1079.65</v>
+      </c>
       <c r="F191" s="10" t="n">
-        <v>1079.65</v>
-      </c>
-      <c r="G191" s="10" t="n">
         <v>826.25</v>
       </c>
-      <c r="H191" s="10" t="inlineStr">
+      <c r="G191" s="10" t="inlineStr">
         <is>
           <t>+76.5%</t>
         </is>
       </c>
-      <c r="I191" s="11" t="inlineStr">
+      <c r="H191" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4641,15 +4410,12 @@
         <v>299.32</v>
       </c>
       <c r="E194" s="9" t="n">
-        <v>299.32</v>
+        <v>182.68</v>
       </c>
       <c r="F194" s="9" t="n">
-        <v>182.68</v>
-      </c>
-      <c r="G194" s="9" t="n">
         <v>116.64</v>
       </c>
-      <c r="H194" s="9" t="inlineStr">
+      <c r="G194" s="9" t="inlineStr">
         <is>
           <t>+63.9%</t>
         </is>
@@ -4664,23 +4430,23 @@
       <c r="D195" s="10" t="n">
         <v>453.63</v>
       </c>
+      <c r="E195" s="10" t="n">
+        <v>241.9</v>
+      </c>
       <c r="F195" s="10" t="n">
-        <v>241.9</v>
-      </c>
-      <c r="G195" s="10" t="n">
         <v>211.73</v>
       </c>
-      <c r="H195" s="10" t="inlineStr">
+      <c r="G195" s="10" t="inlineStr">
         <is>
           <t>+87.5%</t>
         </is>
       </c>
-      <c r="I195" s="11" t="inlineStr">
+      <c r="H195" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J195" s="16" t="inlineStr">
+      <c r="I195" s="16" t="inlineStr">
         <is>
           <t>Job 236355: invoiced $242, actual cost $194 → margin +20%</t>
         </is>
@@ -4711,17 +4477,14 @@
         <v>876.4400000000001</v>
       </c>
       <c r="E198" s="9" t="n">
-        <v>8.763999999999999</v>
+        <v>865.79</v>
       </c>
       <c r="F198" s="9" t="n">
-        <v>889.29</v>
-      </c>
-      <c r="G198" s="9" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="H198" s="9" t="inlineStr">
-        <is>
-          <t>-1.4%</t>
+        <v>10.65</v>
+      </c>
+      <c r="G198" s="9" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
         </is>
       </c>
     </row>
@@ -4734,18 +4497,18 @@
       <c r="D199" s="10" t="n">
         <v>1361.8</v>
       </c>
+      <c r="E199" s="10" t="n">
+        <v>1230.77</v>
+      </c>
       <c r="F199" s="10" t="n">
-        <v>1230.77</v>
-      </c>
-      <c r="G199" s="10" t="n">
         <v>131.03</v>
       </c>
-      <c r="H199" s="10" t="inlineStr">
+      <c r="G199" s="10" t="inlineStr">
         <is>
           <t>+10.6%</t>
         </is>
       </c>
-      <c r="I199" s="15" t="inlineStr">
+      <c r="H199" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -4776,17 +4539,14 @@
         <v>550.37</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>11.007</v>
+        <v>550.49</v>
       </c>
       <c r="F202" s="9" t="n">
-        <v>573.99</v>
-      </c>
-      <c r="G202" s="9" t="n">
-        <v>-23.62</v>
-      </c>
-      <c r="H202" s="9" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
+        <v>-0.12</v>
+      </c>
+      <c r="G202" s="9" t="inlineStr">
+        <is>
+          <t>-0.0%</t>
         </is>
       </c>
     </row>
@@ -4799,18 +4559,18 @@
       <c r="D203" s="10" t="n">
         <v>1050.73</v>
       </c>
+      <c r="E203" s="10" t="n">
+        <v>724.2</v>
+      </c>
       <c r="F203" s="10" t="n">
-        <v>724.2</v>
-      </c>
-      <c r="G203" s="10" t="n">
         <v>326.53</v>
       </c>
-      <c r="H203" s="10" t="inlineStr">
+      <c r="G203" s="10" t="inlineStr">
         <is>
           <t>+45.1%</t>
         </is>
       </c>
-      <c r="I203" s="11" t="inlineStr">
+      <c r="H203" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -4841,17 +4601,14 @@
         <v>2646.95</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>7.563</v>
+        <v>3336.88</v>
       </c>
       <c r="F206" s="9" t="n">
-        <v>3374.38</v>
-      </c>
-      <c r="G206" s="9" t="n">
-        <v>-727.4299999999999</v>
-      </c>
-      <c r="H206" s="9" t="inlineStr">
-        <is>
-          <t>-21.6%</t>
+        <v>-689.9299999999999</v>
+      </c>
+      <c r="G206" s="9" t="inlineStr">
+        <is>
+          <t>-20.7%</t>
         </is>
       </c>
     </row>
@@ -4873,17 +4630,14 @@
         <v>1864.58</v>
       </c>
       <c r="E207" s="9" t="n">
-        <v>5.327</v>
+        <v>1470.12</v>
       </c>
       <c r="F207" s="9" t="n">
-        <v>1493.62</v>
-      </c>
-      <c r="G207" s="9" t="n">
-        <v>370.96</v>
-      </c>
-      <c r="H207" s="9" t="inlineStr">
-        <is>
-          <t>+24.8%</t>
+        <v>394.46</v>
+      </c>
+      <c r="G207" s="9" t="inlineStr">
+        <is>
+          <t>+26.8%</t>
         </is>
       </c>
     </row>
@@ -4896,18 +4650,18 @@
       <c r="D208" s="10" t="n">
         <v>6591.82</v>
       </c>
+      <c r="E208" s="10" t="n">
+        <v>6766.74</v>
+      </c>
       <c r="F208" s="10" t="n">
-        <v>6766.74</v>
-      </c>
-      <c r="G208" s="10" t="n">
         <v>-174.92</v>
       </c>
-      <c r="H208" s="10" t="inlineStr">
+      <c r="G208" s="10" t="inlineStr">
         <is>
           <t>-2.6%</t>
         </is>
       </c>
-      <c r="I208" s="12" t="inlineStr">
+      <c r="H208" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4938,17 +4692,14 @@
         <v>127.81</v>
       </c>
       <c r="E211" s="9" t="n">
-        <v>2.556</v>
+        <v>199.16</v>
       </c>
       <c r="F211" s="9" t="n">
-        <v>222.66</v>
-      </c>
-      <c r="G211" s="9" t="n">
-        <v>-94.84999999999999</v>
-      </c>
-      <c r="H211" s="9" t="inlineStr">
-        <is>
-          <t>-42.6%</t>
+        <v>-71.34999999999999</v>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>-35.8%</t>
         </is>
       </c>
     </row>
@@ -4961,23 +4712,23 @@
       <c r="D212" s="10" t="n">
         <v>255.63</v>
       </c>
+      <c r="E212" s="10" t="n">
+        <v>248.28</v>
+      </c>
       <c r="F212" s="10" t="n">
-        <v>248.28</v>
-      </c>
-      <c r="G212" s="10" t="n">
         <v>7.35</v>
       </c>
-      <c r="H212" s="10" t="inlineStr">
+      <c r="G212" s="10" t="inlineStr">
         <is>
           <t>+3.0%</t>
         </is>
       </c>
-      <c r="I212" s="12" t="inlineStr">
+      <c r="H212" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J212" s="16" t="inlineStr">
+      <c r="I212" s="16" t="inlineStr">
         <is>
           <t>Job 236688: invoiced $248, actual cost $207 → margin +17%</t>
         </is>
@@ -5008,17 +4759,14 @@
         <v>4398.3</v>
       </c>
       <c r="E215" s="9" t="n">
-        <v>19.992</v>
+        <v>4298.93</v>
       </c>
       <c r="F215" s="9" t="n">
-        <v>4386.16</v>
-      </c>
-      <c r="G215" s="9" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="H215" s="9" t="inlineStr">
-        <is>
-          <t>+0.3%</t>
+        <v>99.37</v>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>+2.3%</t>
         </is>
       </c>
     </row>
@@ -5031,23 +4779,23 @@
       <c r="D216" s="10" t="n">
         <v>5824.4</v>
       </c>
+      <c r="E216" s="10" t="n">
+        <v>6164.32</v>
+      </c>
       <c r="F216" s="10" t="n">
-        <v>6164.32</v>
-      </c>
-      <c r="G216" s="10" t="n">
         <v>-339.92</v>
       </c>
-      <c r="H216" s="10" t="inlineStr">
+      <c r="G216" s="10" t="inlineStr">
         <is>
           <t>-5.5%</t>
         </is>
       </c>
-      <c r="I216" s="12" t="inlineStr">
+      <c r="H216" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J216" s="16" t="inlineStr">
+      <c r="I216" s="16" t="inlineStr">
         <is>
           <t>Job 236802: invoiced $6,164, actual cost $4,859 → margin +21%</t>
         </is>
@@ -5078,17 +4826,14 @@
         <v>1192.05</v>
       </c>
       <c r="E219" s="9" t="n">
-        <v>5.183</v>
+        <v>919.67</v>
       </c>
       <c r="F219" s="9" t="n">
-        <v>943.17</v>
-      </c>
-      <c r="G219" s="9" t="n">
-        <v>248.88</v>
-      </c>
-      <c r="H219" s="9" t="inlineStr">
-        <is>
-          <t>+26.4%</t>
+        <v>272.38</v>
+      </c>
+      <c r="G219" s="9" t="inlineStr">
+        <is>
+          <t>+29.6%</t>
         </is>
       </c>
     </row>
@@ -5101,23 +4846,23 @@
       <c r="D220" s="10" t="n">
         <v>1753.9</v>
       </c>
+      <c r="E220" s="10" t="n">
+        <v>1387.27</v>
+      </c>
       <c r="F220" s="10" t="n">
-        <v>1387.27</v>
-      </c>
-      <c r="G220" s="10" t="n">
         <v>366.63</v>
       </c>
-      <c r="H220" s="10" t="inlineStr">
+      <c r="G220" s="10" t="inlineStr">
         <is>
           <t>+26.4%</t>
         </is>
       </c>
-      <c r="I220" s="11" t="inlineStr">
+      <c r="H220" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J220" s="13" t="inlineStr">
+      <c r="I220" s="13" t="inlineStr">
         <is>
           <t>Job 236550: invoiced $1,387, actual cost $1,631 → margin -18%</t>
         </is>
@@ -5148,17 +4893,14 @@
         <v>937.84</v>
       </c>
       <c r="E223" s="9" t="n">
-        <v>12.505</v>
+        <v>743.38</v>
       </c>
       <c r="F223" s="9" t="n">
-        <v>766.88</v>
-      </c>
-      <c r="G223" s="9" t="n">
-        <v>170.96</v>
-      </c>
-      <c r="H223" s="9" t="inlineStr">
-        <is>
-          <t>+22.3%</t>
+        <v>194.46</v>
+      </c>
+      <c r="G223" s="9" t="inlineStr">
+        <is>
+          <t>+26.2%</t>
         </is>
       </c>
     </row>
@@ -5180,17 +4922,14 @@
         <v>1499.62</v>
       </c>
       <c r="E224" s="9" t="n">
-        <v>9.997</v>
+        <v>1280.13</v>
       </c>
       <c r="F224" s="9" t="n">
-        <v>1303.63</v>
-      </c>
-      <c r="G224" s="9" t="n">
-        <v>195.99</v>
-      </c>
-      <c r="H224" s="9" t="inlineStr">
-        <is>
-          <t>+15.0%</t>
+        <v>219.49</v>
+      </c>
+      <c r="G224" s="9" t="inlineStr">
+        <is>
+          <t>+17.1%</t>
         </is>
       </c>
     </row>
@@ -5203,18 +4942,18 @@
       <c r="D225" s="10" t="n">
         <v>3798.03</v>
       </c>
+      <c r="E225" s="10" t="n">
+        <v>3134.12</v>
+      </c>
       <c r="F225" s="10" t="n">
-        <v>3134.12</v>
-      </c>
-      <c r="G225" s="10" t="n">
         <v>663.91</v>
       </c>
-      <c r="H225" s="10" t="inlineStr">
+      <c r="G225" s="10" t="inlineStr">
         <is>
           <t>+21.2%</t>
         </is>
       </c>
-      <c r="I225" s="11" t="inlineStr">
+      <c r="H225" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5245,17 +4984,14 @@
         <v>702.2</v>
       </c>
       <c r="E228" s="9" t="n">
-        <v>1.404</v>
+        <v>610.12</v>
       </c>
       <c r="F228" s="9" t="n">
-        <v>633.62</v>
-      </c>
-      <c r="G228" s="9" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="H228" s="9" t="inlineStr">
-        <is>
-          <t>+10.8%</t>
+        <v>92.08</v>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>+15.1%</t>
         </is>
       </c>
     </row>
@@ -5268,23 +5004,23 @@
       <c r="D229" s="10" t="n">
         <v>1259.41</v>
       </c>
+      <c r="E229" s="10" t="n">
+        <v>985.09</v>
+      </c>
       <c r="F229" s="10" t="n">
-        <v>985.09</v>
-      </c>
-      <c r="G229" s="10" t="n">
         <v>274.32</v>
       </c>
-      <c r="H229" s="10" t="inlineStr">
+      <c r="G229" s="10" t="inlineStr">
         <is>
           <t>+27.8%</t>
         </is>
       </c>
-      <c r="I229" s="11" t="inlineStr">
+      <c r="H229" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J229" s="16" t="inlineStr">
+      <c r="I229" s="16" t="inlineStr">
         <is>
           <t>Job 236822: invoiced $985, actual cost $926 → margin +6%</t>
         </is>
@@ -5315,17 +5051,14 @@
         <v>2205.73</v>
       </c>
       <c r="E232" s="9" t="n">
-        <v>0.1</v>
+        <v>1625.14</v>
       </c>
       <c r="F232" s="9" t="n">
-        <v>1723.89</v>
-      </c>
-      <c r="G232" s="9" t="n">
-        <v>481.84</v>
-      </c>
-      <c r="H232" s="9" t="inlineStr">
-        <is>
-          <t>+28.0%</t>
+        <v>580.59</v>
+      </c>
+      <c r="G232" s="9" t="inlineStr">
+        <is>
+          <t>+35.7%</t>
         </is>
       </c>
     </row>
@@ -5338,18 +5071,18 @@
       <c r="D233" s="10" t="n">
         <v>3416.08</v>
       </c>
+      <c r="E233" s="10" t="n">
+        <v>2279.73</v>
+      </c>
       <c r="F233" s="10" t="n">
-        <v>2279.73</v>
-      </c>
-      <c r="G233" s="10" t="n">
         <v>1136.35</v>
       </c>
-      <c r="H233" s="10" t="inlineStr">
+      <c r="G233" s="10" t="inlineStr">
         <is>
           <t>+49.8%</t>
         </is>
       </c>
-      <c r="I233" s="11" t="inlineStr">
+      <c r="H233" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5380,17 +5113,14 @@
         <v>1066.87</v>
       </c>
       <c r="E236" s="9" t="n">
-        <v>2.134</v>
+        <v>851.6799999999999</v>
       </c>
       <c r="F236" s="9" t="n">
-        <v>875.1799999999999</v>
-      </c>
-      <c r="G236" s="9" t="n">
-        <v>191.68</v>
-      </c>
-      <c r="H236" s="9" t="inlineStr">
-        <is>
-          <t>+21.9%</t>
+        <v>215.18</v>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>+25.3%</t>
         </is>
       </c>
     </row>
@@ -5403,18 +5133,18 @@
       <c r="D237" s="10" t="n">
         <v>1668.47</v>
       </c>
+      <c r="E237" s="10" t="n">
+        <v>1221.28</v>
+      </c>
       <c r="F237" s="10" t="n">
-        <v>1221.28</v>
-      </c>
-      <c r="G237" s="10" t="n">
         <v>447.19</v>
       </c>
-      <c r="H237" s="10" t="inlineStr">
+      <c r="G237" s="10" t="inlineStr">
         <is>
           <t>+36.6%</t>
         </is>
       </c>
-      <c r="I237" s="11" t="inlineStr">
+      <c r="H237" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5445,17 +5175,14 @@
         <v>275.89</v>
       </c>
       <c r="E240" s="9" t="n">
-        <v>275.89</v>
+        <v>135.72</v>
       </c>
       <c r="F240" s="9" t="n">
-        <v>147.22</v>
-      </c>
-      <c r="G240" s="9" t="n">
-        <v>128.67</v>
-      </c>
-      <c r="H240" s="9" t="inlineStr">
-        <is>
-          <t>+87.4%</t>
+        <v>140.17</v>
+      </c>
+      <c r="G240" s="9" t="inlineStr">
+        <is>
+          <t>+103.3%</t>
         </is>
       </c>
     </row>
@@ -5477,17 +5204,14 @@
         <v>275.89</v>
       </c>
       <c r="E241" s="9" t="n">
-        <v>275.89</v>
+        <v>135.72</v>
       </c>
       <c r="F241" s="9" t="n">
-        <v>147.22</v>
-      </c>
-      <c r="G241" s="9" t="n">
-        <v>128.67</v>
-      </c>
-      <c r="H241" s="9" t="inlineStr">
-        <is>
-          <t>+87.4%</t>
+        <v>140.17</v>
+      </c>
+      <c r="G241" s="9" t="inlineStr">
+        <is>
+          <t>+103.3%</t>
         </is>
       </c>
     </row>
@@ -5509,17 +5233,14 @@
         <v>283.79</v>
       </c>
       <c r="E242" s="9" t="n">
-        <v>283.79</v>
+        <v>198.46</v>
       </c>
       <c r="F242" s="9" t="n">
-        <v>209.96</v>
-      </c>
-      <c r="G242" s="9" t="n">
-        <v>73.83</v>
-      </c>
-      <c r="H242" s="9" t="inlineStr">
-        <is>
-          <t>+35.2%</t>
+        <v>85.33</v>
+      </c>
+      <c r="G242" s="9" t="inlineStr">
+        <is>
+          <t>+43.0%</t>
         </is>
       </c>
     </row>
@@ -5532,18 +5253,18 @@
       <c r="D243" s="10" t="n">
         <v>1331.14</v>
       </c>
+      <c r="E243" s="10" t="n">
+        <v>906.92</v>
+      </c>
       <c r="F243" s="10" t="n">
-        <v>906.92</v>
-      </c>
-      <c r="G243" s="10" t="n">
         <v>424.22</v>
       </c>
-      <c r="H243" s="10" t="inlineStr">
+      <c r="G243" s="10" t="inlineStr">
         <is>
           <t>+46.8%</t>
         </is>
       </c>
-      <c r="I243" s="11" t="inlineStr">
+      <c r="H243" s="11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -5574,17 +5295,14 @@
         <v>2134.98</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>8.539999999999999</v>
+        <v>1666.48</v>
       </c>
       <c r="F246" s="9" t="n">
-        <v>1689.98</v>
-      </c>
-      <c r="G246" s="9" t="n">
-        <v>445</v>
-      </c>
-      <c r="H246" s="9" t="inlineStr">
-        <is>
-          <t>+26.3%</t>
+        <v>468.5</v>
+      </c>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>+28.1%</t>
         </is>
       </c>
     </row>
@@ -5597,23 +5315,23 @@
       <c r="D247" s="10" t="n">
         <v>3071.43</v>
       </c>
+      <c r="E247" s="10" t="n">
+        <v>2749.42</v>
+      </c>
       <c r="F247" s="10" t="n">
-        <v>2749.42</v>
-      </c>
-      <c r="G247" s="10" t="n">
         <v>322.01</v>
       </c>
-      <c r="H247" s="10" t="inlineStr">
+      <c r="G247" s="10" t="inlineStr">
         <is>
           <t>+11.7%</t>
         </is>
       </c>
-      <c r="I247" s="15" t="inlineStr">
+      <c r="H247" s="15" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="J247" s="16" t="inlineStr">
+      <c r="I247" s="16" t="inlineStr">
         <is>
           <t>Job 236869: invoiced $2,876, actual cost $2,580 → margin +10%</t>
         </is>
@@ -5621,56 +5339,56 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A85:J85"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A135:J135"/>
-    <mergeCell ref="A188:J188"/>
-    <mergeCell ref="A131:J131"/>
-    <mergeCell ref="A184:J184"/>
-    <mergeCell ref="A231:J231"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A180:J180"/>
-    <mergeCell ref="A210:J210"/>
-    <mergeCell ref="A156:J156"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A152:J152"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A127:J127"/>
-    <mergeCell ref="A143:J143"/>
-    <mergeCell ref="A245:J245"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A148:J148"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A201:J201"/>
-    <mergeCell ref="A222:J222"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A98:J98"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A94:J94"/>
-    <mergeCell ref="A103:J103"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A123:J123"/>
-    <mergeCell ref="A168:J168"/>
-    <mergeCell ref="A197:J197"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A227:J227"/>
-    <mergeCell ref="A218:J218"/>
-    <mergeCell ref="A205:J205"/>
-    <mergeCell ref="A108:J108"/>
-    <mergeCell ref="A193:J193"/>
-    <mergeCell ref="A118:J118"/>
-    <mergeCell ref="A89:J89"/>
-    <mergeCell ref="A214:J214"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A139:J139"/>
-    <mergeCell ref="A239:J239"/>
-    <mergeCell ref="A113:J113"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A235:J235"/>
+    <mergeCell ref="A227:I227"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="A193:I193"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A214:I214"/>
+    <mergeCell ref="A239:I239"/>
+    <mergeCell ref="A139:I139"/>
+    <mergeCell ref="A210:I210"/>
+    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A235:I235"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A188:I188"/>
+    <mergeCell ref="A135:I135"/>
+    <mergeCell ref="A184:I184"/>
+    <mergeCell ref="A131:I131"/>
+    <mergeCell ref="A231:I231"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A180:I180"/>
+    <mergeCell ref="A156:I156"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A152:I152"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="A245:I245"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A201:I201"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A148:I148"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A222:I222"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="A197:I197"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A168:I168"/>
+    <mergeCell ref="A218:I218"/>
+    <mergeCell ref="A205:I205"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
